--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A460FCCE-653D-4E3E-A698-16A782709FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0733D89-1959-4727-BD2F-35E3271A283C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12328,7 +12328,10 @@
       <c r="C8" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="D8" s="72"/>
+      <c r="D8" s="72">
+        <f ca="1">TODAY()</f>
+        <v>46294</v>
+      </c>
       <c r="F8" s="38" t="s">
         <v>117</v>
       </c>
@@ -12340,7 +12343,10 @@
       <c r="C9" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="D9" s="40"/>
+      <c r="D9" s="40">
+        <f ca="1">NOW()</f>
+        <v>46294.089271874996</v>
+      </c>
     </row>
     <row r="12" spans="2:7" ht="18" x14ac:dyDescent="0.35">
       <c r="B12" s="39" t="s">

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0733D89-1959-4727-BD2F-35E3271A283C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D544EA-CDE1-4582-A97B-3F3A65C7D805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12345,7 +12345,7 @@
       </c>
       <c r="D9" s="40">
         <f ca="1">NOW()</f>
-        <v>46294.089271874996</v>
+        <v>46294.09043773148</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="18" x14ac:dyDescent="0.35">
@@ -12355,7 +12355,10 @@
       <c r="C12" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="39"/>
+      <c r="D12" s="39">
+        <f ca="1">DAY(D8)</f>
+        <v>29</v>
+      </c>
       <c r="F12" s="38" t="s">
         <v>110</v>
       </c>
@@ -12368,7 +12371,10 @@
       <c r="C13" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="D13" s="39"/>
+      <c r="D13" s="39">
+        <f ca="1">MONTH(D8)</f>
+        <v>9</v>
+      </c>
     </row>
     <row r="14" spans="2:7" ht="18" x14ac:dyDescent="0.35">
       <c r="B14" s="39" t="s">
@@ -12377,7 +12383,10 @@
       <c r="C14" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="D14" s="39"/>
+      <c r="D14" s="39">
+        <f ca="1">YEAR(D8)</f>
+        <v>2026</v>
+      </c>
     </row>
     <row r="17" spans="2:9" ht="18" x14ac:dyDescent="0.35">
       <c r="B17" s="39" t="s">
@@ -12386,7 +12395,10 @@
       <c r="C17" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="39"/>
+      <c r="D17" s="39">
+        <f>DATEDIF(H18,H17,"y")</f>
+        <v>2</v>
+      </c>
       <c r="F17" s="38" t="s">
         <v>111</v>
       </c>

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D544EA-CDE1-4582-A97B-3F3A65C7D805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7416208-9658-4E6F-9A66-6AD9A6FA058C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12345,7 +12345,7 @@
       </c>
       <c r="D9" s="40">
         <f ca="1">NOW()</f>
-        <v>46294.09043773148</v>
+        <v>46294.091625000001</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="18" x14ac:dyDescent="0.35">
@@ -12416,7 +12416,10 @@
       <c r="C18" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="39"/>
+      <c r="D18" s="39">
+        <f>NETWORKDAYS(H18,H17)</f>
+        <v>715</v>
+      </c>
       <c r="H18" s="42">
         <v>45375</v>
       </c>
@@ -12431,7 +12434,10 @@
       <c r="C19" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="D19" s="44"/>
+      <c r="D19" s="44">
+        <f>NETWORKDAYS.INTL(H18,H17,1)</f>
+        <v>715</v>
+      </c>
     </row>
     <row r="22" spans="2:9" ht="18" x14ac:dyDescent="0.35">
       <c r="B22" s="39" t="s">
@@ -12440,7 +12446,10 @@
       <c r="C22" s="41" t="s">
         <v>132</v>
       </c>
-      <c r="D22" s="39"/>
+      <c r="D22" s="39">
+        <f ca="1">WEEKDAY(D8)</f>
+        <v>3</v>
+      </c>
       <c r="F22" s="38" t="s">
         <v>131</v>
       </c>
@@ -12452,7 +12461,10 @@
       <c r="C23" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="D23" s="39"/>
+      <c r="D23" s="39">
+        <f ca="1">WEEKNUM(D8)</f>
+        <v>40</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7416208-9658-4E6F-9A66-6AD9A6FA058C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52FCB38D-4351-4167-B831-70D75D935085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Date and Time " sheetId="19" r:id="rId1"/>
@@ -12345,7 +12345,7 @@
       </c>
       <c r="D9" s="40">
         <f ca="1">NOW()</f>
-        <v>46294.091625000001</v>
+        <v>46294.093220717594</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="18" x14ac:dyDescent="0.35">
@@ -12595,10 +12595,7 @@
         <f>OR(C27&gt;80,C28&gt;80)</f>
         <v>1</v>
       </c>
-      <c r="K27" s="32" t="b">
-        <f>NOT(J27)</f>
-        <v>0</v>
-      </c>
+      <c r="K27" s="32"/>
       <c r="L27" s="32" t="str" cm="1">
         <f t="array" ref="L27">_xlfn.SWITCH(C27,60,"good",70,"ex",50,"right")</f>
         <v>good</v>
@@ -12639,10 +12636,7 @@
         <f t="shared" ref="J28:J38" si="2">OR(C28&gt;80,C29&gt;80)</f>
         <v>1</v>
       </c>
-      <c r="K28" s="32" t="b">
-        <f t="shared" ref="K28:K38" si="3">NOT(J28)</f>
-        <v>0</v>
-      </c>
+      <c r="K28" s="32"/>
       <c r="L28" s="32" t="e" cm="1">
         <f t="array" ref="L28">_xlfn.SWITCH(C28,60,"good",70,"ex",50,"right")</f>
         <v>#N/A</v>
@@ -12662,7 +12656,7 @@
         <v>34</v>
       </c>
       <c r="D29" s="30" t="e">
-        <f t="shared" ref="D29:D38" si="4">C29/0</f>
+        <f t="shared" ref="D29:D38" si="3">C29/0</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E29" s="31" t="b">
@@ -12683,10 +12677,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K29" s="32" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
+      <c r="K29" s="32"/>
       <c r="L29" s="32" t="e" cm="1">
         <f t="array" ref="L29">_xlfn.SWITCH(C29,60,"good",70,"ex",50,"right")</f>
         <v>#N/A</v>
@@ -12706,7 +12697,7 @@
         <v>76</v>
       </c>
       <c r="D30" s="30" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E30" s="31" t="b">
@@ -12727,10 +12718,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K30" s="32" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
+      <c r="K30" s="32"/>
       <c r="L30" s="32" t="e" cm="1">
         <f t="array" ref="L30">_xlfn.SWITCH(C30,60,"good",70,"ex",50,"right")</f>
         <v>#N/A</v>
@@ -12771,10 +12759,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K31" s="32" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="K31" s="32"/>
       <c r="L31" s="32" t="e" cm="1">
         <f t="array" ref="L31">_xlfn.SWITCH(C31,60,"good",70,"ex",50,"right")</f>
         <v>#N/A</v>
@@ -12792,7 +12777,7 @@
         <v>95</v>
       </c>
       <c r="D32" s="30" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E32" s="31" t="str">
@@ -12813,10 +12798,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K32" s="32" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="K32" s="32"/>
       <c r="L32" s="32" t="e" cm="1">
         <f t="array" ref="L32">_xlfn.SWITCH(C32,60,"good",70,"ex",50,"right")</f>
         <v>#N/A</v>
@@ -12853,10 +12835,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K33" s="32" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="K33" s="32"/>
       <c r="L33" s="32" t="str" cm="1">
         <f t="array" ref="L33">_xlfn.SWITCH(C33,60,"good",70,"ex",50,"right")</f>
         <v>right</v>
@@ -12876,7 +12855,7 @@
         <v>87</v>
       </c>
       <c r="D34" s="30" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E34" s="31" t="str">
@@ -12897,10 +12876,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K34" s="32" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="K34" s="32"/>
       <c r="L34" s="32" t="e" cm="1">
         <f t="array" ref="L34">_xlfn.SWITCH(C34,60,"good",70,"ex",50,"right")</f>
         <v>#N/A</v>
@@ -12941,10 +12917,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K35" s="32" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
+      <c r="K35" s="32"/>
       <c r="L35" s="32" t="e" cm="1">
         <f t="array" ref="L35">_xlfn.SWITCH(C35,60,"good",70,"ex",50,"right")</f>
         <v>#N/A</v>
@@ -12964,7 +12937,7 @@
         <v>66</v>
       </c>
       <c r="D36" s="30" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E36" s="31" t="b">
@@ -12985,10 +12958,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K36" s="32" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
+      <c r="K36" s="32"/>
       <c r="L36" s="32" t="e" cm="1">
         <f t="array" ref="L36">_xlfn.SWITCH(C36,60,"good",70,"ex",50,"right")</f>
         <v>#N/A</v>
@@ -13029,10 +12999,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K37" s="32" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
+      <c r="K37" s="32"/>
       <c r="L37" s="32" t="e" cm="1">
         <f t="array" ref="L37">_xlfn.SWITCH(C37,60,"good",70,"ex",50,"right")</f>
         <v>#N/A</v>
@@ -13046,7 +13013,7 @@
         <v>73</v>
       </c>
       <c r="D38" s="30" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E38" s="31" t="b">
@@ -13067,10 +13034,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K38" s="32" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
+      <c r="K38" s="32"/>
       <c r="L38" s="32" t="e" cm="1">
         <f t="array" ref="L38">_xlfn.SWITCH(C38,60,"good",70,"ex",50,"right")</f>
         <v>#N/A</v>

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52FCB38D-4351-4167-B831-70D75D935085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D792A6-A176-4B0C-BF8B-207B4B8C3820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,28 +56,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1732,7 +1710,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>693420</xdr:colOff>
+      <xdr:colOff>750570</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
@@ -1793,7 +1771,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>175260</xdr:colOff>
+      <xdr:colOff>470535</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
@@ -1853,8 +1831,8 @@
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
@@ -12345,7 +12323,7 @@
       </c>
       <c r="D9" s="40">
         <f ca="1">NOW()</f>
-        <v>46294.093220717594</v>
+        <v>46294.097648958334</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="18" x14ac:dyDescent="0.35">
@@ -12480,17 +12458,17 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.33203125" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" customWidth="1"/>
-    <col min="4" max="4" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" customWidth="1"/>
     <col min="7" max="7" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" customWidth="1"/>
-    <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" customWidth="1"/>
+    <col min="8" max="8" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.109375" customWidth="1"/>
+    <col min="11" max="11" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12573,33 +12551,18 @@
       <c r="C27" s="30">
         <v>60</v>
       </c>
-      <c r="D27" s="30" t="e">
-        <f>C27/0</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E27" s="31" t="b">
-        <f>IF(C27&gt;80,"Ex")</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="32" t="str" cm="1">
-        <f t="array" ref="F27">_xlfn.IFS(C27&gt;F4660,"faild",C27&gt;90,"ex",C27&gt;80,"vg",C27&gt;70,"g",C27&gt;60,"pass")</f>
-        <v>faild</v>
-      </c>
-      <c r="G27" s="50" t="str">
-        <f>IFERROR(D27,"its error")</f>
-        <v>its error</v>
-      </c>
+      <c r="D27" s="30"/>
+      <c r="E27" s="31" t="str">
+        <f>IF(C27&gt;80, "Passed", "Failed")</f>
+        <v>Failed</v>
+      </c>
+      <c r="F27" s="32"/>
+      <c r="G27" s="50"/>
       <c r="H27" s="32"/>
       <c r="I27" s="32"/>
-      <c r="J27" s="32" t="b">
-        <f>OR(C27&gt;80,C28&gt;80)</f>
-        <v>1</v>
-      </c>
+      <c r="J27" s="32"/>
       <c r="K27" s="32"/>
-      <c r="L27" s="32" t="str" cm="1">
-        <f t="array" ref="L27">_xlfn.SWITCH(C27,60,"good",70,"ex",50,"right")</f>
-        <v>good</v>
-      </c>
+      <c r="L27" s="32"/>
       <c r="N27" s="33" t="s">
         <v>89</v>
       </c>
@@ -12614,33 +12577,18 @@
       <c r="C28" s="29">
         <v>81</v>
       </c>
-      <c r="D28" s="55" t="e">
-        <f>NA()</f>
-        <v>#N/A</v>
-      </c>
+      <c r="D28" s="55"/>
       <c r="E28" s="31" t="str">
-        <f t="shared" ref="E28:E38" si="0">IF(C28&gt;80,"Ex")</f>
-        <v>Ex</v>
-      </c>
-      <c r="F28" s="32" t="str" cm="1">
-        <f t="array" ref="F28">_xlfn.IFS(C28&gt;60,"pass",C28&gt;90,"ex",C28&gt;80,"vg",C28&gt;70,"g",C28&lt;60,"faild")</f>
-        <v>pass</v>
-      </c>
-      <c r="G28" s="50" t="str">
-        <f t="shared" ref="G28:G38" si="1">IFERROR(D28,"its error")</f>
-        <v>its error</v>
-      </c>
+        <f t="shared" ref="E28:E38" si="0">IF(C28&gt;80, "Passed", "Failed")</f>
+        <v>Passed</v>
+      </c>
+      <c r="F28" s="32"/>
+      <c r="G28" s="50"/>
       <c r="H28" s="32"/>
       <c r="I28" s="32"/>
-      <c r="J28" s="32" t="b">
-        <f t="shared" ref="J28:J38" si="2">OR(C28&gt;80,C29&gt;80)</f>
-        <v>1</v>
-      </c>
+      <c r="J28" s="32"/>
       <c r="K28" s="32"/>
-      <c r="L28" s="32" t="e" cm="1">
-        <f t="array" ref="L28">_xlfn.SWITCH(C28,60,"good",70,"ex",50,"right")</f>
-        <v>#N/A</v>
-      </c>
+      <c r="L28" s="32"/>
       <c r="N28" s="33" t="s">
         <v>91</v>
       </c>
@@ -12655,33 +12603,18 @@
       <c r="C29" s="29">
         <v>34</v>
       </c>
-      <c r="D29" s="30" t="e">
-        <f t="shared" ref="D29:D38" si="3">C29/0</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E29" s="31" t="b">
+      <c r="D29" s="30"/>
+      <c r="E29" s="31" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="32" t="str" cm="1">
-        <f t="array" ref="F29">_xlfn.IFS(C29&gt;90,"ex",C29&gt;80,"vg",C29&gt;70,"g",C29&gt;60,"pass",C29&lt;60,"faild")</f>
-        <v>faild</v>
-      </c>
-      <c r="G29" s="50" t="str">
-        <f t="shared" si="1"/>
-        <v>its error</v>
-      </c>
+        <v>Failed</v>
+      </c>
+      <c r="F29" s="32"/>
+      <c r="G29" s="50"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
-      <c r="J29" s="32" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J29" s="32"/>
       <c r="K29" s="32"/>
-      <c r="L29" s="32" t="e" cm="1">
-        <f t="array" ref="L29">_xlfn.SWITCH(C29,60,"good",70,"ex",50,"right")</f>
-        <v>#N/A</v>
-      </c>
+      <c r="L29" s="32"/>
       <c r="N29" s="33" t="s">
         <v>93</v>
       </c>
@@ -12696,33 +12629,18 @@
       <c r="C30" s="29">
         <v>76</v>
       </c>
-      <c r="D30" s="30" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E30" s="31" t="b">
+      <c r="D30" s="30"/>
+      <c r="E30" s="31" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F30" s="32" t="str" cm="1">
-        <f t="array" ref="F30">_xlfn.IFS(C30&gt;90,"ex",C30&gt;80,"vg",C30&gt;70,"g",C30&gt;60,"pass",C30&lt;60,"faild")</f>
-        <v>g</v>
-      </c>
-      <c r="G30" s="50" t="str">
-        <f t="shared" si="1"/>
-        <v>its error</v>
-      </c>
+        <v>Failed</v>
+      </c>
+      <c r="F30" s="32"/>
+      <c r="G30" s="50"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
-      <c r="J30" s="32" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J30" s="32"/>
       <c r="K30" s="32"/>
-      <c r="L30" s="32" t="e" cm="1">
-        <f t="array" ref="L30">_xlfn.SWITCH(C30,60,"good",70,"ex",50,"right")</f>
-        <v>#N/A</v>
-      </c>
+      <c r="L30" s="32"/>
       <c r="N30" s="33" t="s">
         <v>95</v>
       </c>
@@ -12737,33 +12655,18 @@
       <c r="C31" s="29">
         <v>64</v>
       </c>
-      <c r="D31" s="55" t="e">
-        <f>NA()</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E31" s="31" t="b">
+      <c r="D31" s="55"/>
+      <c r="E31" s="31" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F31" s="32" t="str" cm="1">
-        <f t="array" ref="F31">_xlfn.IFS(C31&gt;90,"ex",C31&gt;80,"vg",C31&gt;70,"g",C31&gt;60,"pass",C31&lt;60,"faild")</f>
-        <v>pass</v>
-      </c>
-      <c r="G31" s="50" t="str">
-        <f t="shared" si="1"/>
-        <v>its error</v>
-      </c>
+        <v>Failed</v>
+      </c>
+      <c r="F31" s="32"/>
+      <c r="G31" s="50"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
-      <c r="J31" s="32" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="J31" s="32"/>
       <c r="K31" s="32"/>
-      <c r="L31" s="32" t="e" cm="1">
-        <f t="array" ref="L31">_xlfn.SWITCH(C31,60,"good",70,"ex",50,"right")</f>
-        <v>#N/A</v>
-      </c>
+      <c r="L31" s="32"/>
       <c r="N31" s="33"/>
       <c r="O31" s="33" t="s">
         <v>97</v>
@@ -12776,33 +12679,18 @@
       <c r="C32" s="29">
         <v>95</v>
       </c>
-      <c r="D32" s="30" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="D32" s="30"/>
       <c r="E32" s="31" t="str">
         <f t="shared" si="0"/>
-        <v>Ex</v>
-      </c>
-      <c r="F32" s="32" t="str" cm="1">
-        <f t="array" ref="F32">_xlfn.IFS(C32&gt;90,"ex",C32&gt;80,"vg",C32&gt;70,"g",C32&gt;60,"pass",C32&lt;60,"faild")</f>
-        <v>ex</v>
-      </c>
-      <c r="G32" s="50" t="str">
-        <f t="shared" si="1"/>
-        <v>its error</v>
-      </c>
+        <v>Passed</v>
+      </c>
+      <c r="F32" s="32"/>
+      <c r="G32" s="50"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
-      <c r="J32" s="32" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="J32" s="32"/>
       <c r="K32" s="32"/>
-      <c r="L32" s="32" t="e" cm="1">
-        <f t="array" ref="L32">_xlfn.SWITCH(C32,60,"good",70,"ex",50,"right")</f>
-        <v>#N/A</v>
-      </c>
+      <c r="L32" s="32"/>
       <c r="N32" s="34"/>
       <c r="O32" s="34"/>
     </row>
@@ -12813,33 +12701,18 @@
       <c r="C33" s="29">
         <v>50</v>
       </c>
-      <c r="D33" s="55" t="e">
-        <f>NA()</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E33" s="31" t="b">
+      <c r="D33" s="55"/>
+      <c r="E33" s="31" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F33" s="32" t="str" cm="1">
-        <f t="array" ref="F33">_xlfn.IFS(C33&gt;90,"ex",C33&gt;80,"vg",C33&gt;70,"g",C33&gt;60,"pass",C33&lt;60,"faild")</f>
-        <v>faild</v>
-      </c>
-      <c r="G33" s="50" t="str">
-        <f t="shared" si="1"/>
-        <v>its error</v>
-      </c>
+        <v>Failed</v>
+      </c>
+      <c r="F33" s="32"/>
+      <c r="G33" s="50"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
-      <c r="J33" s="32" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="J33" s="32"/>
       <c r="K33" s="32"/>
-      <c r="L33" s="32" t="str" cm="1">
-        <f t="array" ref="L33">_xlfn.SWITCH(C33,60,"good",70,"ex",50,"right")</f>
-        <v>right</v>
-      </c>
+      <c r="L33" s="32"/>
       <c r="N33" s="35" t="s">
         <v>99</v>
       </c>
@@ -12854,33 +12727,18 @@
       <c r="C34" s="29">
         <v>87</v>
       </c>
-      <c r="D34" s="30" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="D34" s="30"/>
       <c r="E34" s="31" t="str">
         <f t="shared" si="0"/>
-        <v>Ex</v>
-      </c>
-      <c r="F34" s="32" t="str" cm="1">
-        <f t="array" ref="F34">_xlfn.IFS(C34&gt;90,"ex",C34&gt;80,"vg",C34&gt;70,"g",C34&gt;60,"pass",C34&lt;60,"faild")</f>
-        <v>vg</v>
-      </c>
-      <c r="G34" s="50" t="str">
-        <f t="shared" si="1"/>
-        <v>its error</v>
-      </c>
+        <v>Passed</v>
+      </c>
+      <c r="F34" s="32"/>
+      <c r="G34" s="50"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
-      <c r="J34" s="32" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="J34" s="32"/>
       <c r="K34" s="32"/>
-      <c r="L34" s="32" t="e" cm="1">
-        <f t="array" ref="L34">_xlfn.SWITCH(C34,60,"good",70,"ex",50,"right")</f>
-        <v>#N/A</v>
-      </c>
+      <c r="L34" s="32"/>
       <c r="N34" s="37" t="s">
         <v>101</v>
       </c>
@@ -12895,33 +12753,18 @@
       <c r="C35" s="29">
         <v>6</v>
       </c>
-      <c r="D35" s="55" t="e">
-        <f>NA()</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E35" s="31" t="b">
+      <c r="D35" s="55"/>
+      <c r="E35" s="31" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F35" s="32" t="str" cm="1">
-        <f t="array" ref="F35">_xlfn.IFS(C35&gt;90,"ex",C35&gt;80,"vg",C35&gt;70,"g",C35&gt;60,"pass",C35&lt;60,"faild")</f>
-        <v>faild</v>
-      </c>
-      <c r="G35" s="50" t="str">
-        <f t="shared" si="1"/>
-        <v>its error</v>
-      </c>
+        <v>Failed</v>
+      </c>
+      <c r="F35" s="32"/>
+      <c r="G35" s="50"/>
       <c r="H35" s="32"/>
       <c r="I35" s="32"/>
-      <c r="J35" s="32" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J35" s="32"/>
       <c r="K35" s="32"/>
-      <c r="L35" s="32" t="e" cm="1">
-        <f t="array" ref="L35">_xlfn.SWITCH(C35,60,"good",70,"ex",50,"right")</f>
-        <v>#N/A</v>
-      </c>
+      <c r="L35" s="32"/>
       <c r="N35" s="37" t="s">
         <v>103</v>
       </c>
@@ -12936,33 +12779,18 @@
       <c r="C36" s="29">
         <v>66</v>
       </c>
-      <c r="D36" s="30" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E36" s="31" t="b">
+      <c r="D36" s="30"/>
+      <c r="E36" s="31" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="32" t="str" cm="1">
-        <f t="array" ref="F36">_xlfn.IFS(C36&gt;90,"ex",C36&gt;80,"vg",C36&gt;70,"g",C36&gt;60,"pass",C36&lt;60,"faild")</f>
-        <v>pass</v>
-      </c>
-      <c r="G36" s="50" t="str">
-        <f t="shared" si="1"/>
-        <v>its error</v>
-      </c>
+        <v>Failed</v>
+      </c>
+      <c r="F36" s="32"/>
+      <c r="G36" s="50"/>
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
-      <c r="J36" s="32" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J36" s="32"/>
       <c r="K36" s="32"/>
-      <c r="L36" s="32" t="e" cm="1">
-        <f t="array" ref="L36">_xlfn.SWITCH(C36,60,"good",70,"ex",50,"right")</f>
-        <v>#N/A</v>
-      </c>
+      <c r="L36" s="32"/>
       <c r="N36" s="37" t="s">
         <v>105</v>
       </c>
@@ -12977,33 +12805,18 @@
       <c r="C37" s="29">
         <v>30</v>
       </c>
-      <c r="D37" s="55" t="e">
-        <f>NA()</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E37" s="31" t="b">
+      <c r="D37" s="55"/>
+      <c r="E37" s="31" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F37" s="32" t="str" cm="1">
-        <f t="array" ref="F37">_xlfn.IFS(C37&gt;90,"ex",C37&gt;80,"vg",C37&gt;70,"g",C37&gt;60,"pass",C37&lt;60,"faild")</f>
-        <v>faild</v>
-      </c>
-      <c r="G37" s="50" t="str">
-        <f t="shared" si="1"/>
-        <v>its error</v>
-      </c>
+        <v>Failed</v>
+      </c>
+      <c r="F37" s="32"/>
+      <c r="G37" s="50"/>
       <c r="H37" s="32"/>
       <c r="I37" s="32"/>
-      <c r="J37" s="32" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J37" s="32"/>
       <c r="K37" s="32"/>
-      <c r="L37" s="32" t="e" cm="1">
-        <f t="array" ref="L37">_xlfn.SWITCH(C37,60,"good",70,"ex",50,"right")</f>
-        <v>#N/A</v>
-      </c>
+      <c r="L37" s="32"/>
     </row>
     <row r="38" spans="2:15" ht="18" x14ac:dyDescent="0.35">
       <c r="B38" s="29" t="s">
@@ -13012,33 +12825,18 @@
       <c r="C38" s="29">
         <v>73</v>
       </c>
-      <c r="D38" s="30" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E38" s="31" t="b">
+      <c r="D38" s="30"/>
+      <c r="E38" s="31" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F38" s="32" t="str" cm="1">
-        <f t="array" ref="F38">_xlfn.IFS(C38&gt;90,"ex",C38&gt;80,"vg",C38&gt;70,"g",C38&gt;60,"pass",C38&lt;60,"faild")</f>
-        <v>g</v>
-      </c>
-      <c r="G38" s="50" t="str">
-        <f t="shared" si="1"/>
-        <v>its error</v>
-      </c>
+        <v>Failed</v>
+      </c>
+      <c r="F38" s="32"/>
+      <c r="G38" s="50"/>
       <c r="H38" s="32"/>
       <c r="I38" s="32"/>
-      <c r="J38" s="32" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="J38" s="32"/>
       <c r="K38" s="32"/>
-      <c r="L38" s="32" t="e" cm="1">
-        <f t="array" ref="L38">_xlfn.SWITCH(C38,60,"good",70,"ex",50,"right")</f>
-        <v>#N/A</v>
-      </c>
+      <c r="L38" s="32"/>
     </row>
     <row r="46" spans="2:15" ht="18" x14ac:dyDescent="0.35">
       <c r="B46" s="38" t="s">

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D792A6-A176-4B0C-BF8B-207B4B8C3820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D256A4F0-966D-49F4-A4A3-D3FBAAE48A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="205">
   <si>
     <t>id</t>
   </si>
@@ -328,25 +328,13 @@
     <t>Ibrahim Bakr</t>
   </si>
   <si>
-    <t>&gt;90</t>
-  </si>
-  <si>
     <t>Ex</t>
   </si>
   <si>
-    <t>&gt;80</t>
-  </si>
-  <si>
     <t>VG</t>
   </si>
   <si>
-    <t>&gt;70</t>
-  </si>
-  <si>
     <t>G</t>
-  </si>
-  <si>
-    <t>&gt;60</t>
   </si>
   <si>
     <t>P</t>
@@ -12291,63 +12279,63 @@
   <sheetData>
     <row r="2" spans="2:7" ht="18" x14ac:dyDescent="0.35">
       <c r="C2" s="38" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="18" x14ac:dyDescent="0.35">
       <c r="C4" s="38" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="18" x14ac:dyDescent="0.35">
       <c r="B8" s="39" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D8" s="72">
         <f ca="1">TODAY()</f>
         <v>46294</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="18" x14ac:dyDescent="0.35">
       <c r="B9" s="39" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D9" s="40">
         <f ca="1">NOW()</f>
-        <v>46294.097648958334</v>
+        <v>46294.100298148151</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="18" x14ac:dyDescent="0.35">
       <c r="B12" s="39" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D12" s="39">
         <f ca="1">DAY(D8)</f>
         <v>29</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G12" s="71"/>
     </row>
     <row r="13" spans="2:7" ht="18" x14ac:dyDescent="0.35">
       <c r="B13" s="39" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D13" s="39">
         <f ca="1">MONTH(D8)</f>
@@ -12356,10 +12344,10 @@
     </row>
     <row r="14" spans="2:7" ht="18" x14ac:dyDescent="0.35">
       <c r="B14" s="39" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D14" s="39">
         <f ca="1">YEAR(D8)</f>
@@ -12368,31 +12356,31 @@
     </row>
     <row r="17" spans="2:9" ht="18" x14ac:dyDescent="0.35">
       <c r="B17" s="39" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D17" s="39">
         <f>DATEDIF(H18,H17,"y")</f>
         <v>2</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H17" s="42">
         <v>46376</v>
       </c>
       <c r="I17" s="43" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="18" x14ac:dyDescent="0.35">
       <c r="B18" s="39" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D18" s="39">
         <f>NETWORKDAYS(H18,H17)</f>
@@ -12402,15 +12390,15 @@
         <v>45375</v>
       </c>
       <c r="I18" s="43" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B19" s="44" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D19" s="44">
         <f>NETWORKDAYS.INTL(H18,H17,1)</f>
@@ -12419,25 +12407,25 @@
     </row>
     <row r="22" spans="2:9" ht="18" x14ac:dyDescent="0.35">
       <c r="B22" s="39" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D22" s="39">
         <f ca="1">WEEKDAY(D8)</f>
         <v>3</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="2:9" ht="18" x14ac:dyDescent="0.35">
       <c r="B23" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" s="41" t="s">
         <v>129</v>
-      </c>
-      <c r="C23" s="41" t="s">
-        <v>133</v>
       </c>
       <c r="D23" s="39">
         <f ca="1">WEEKNUM(D8)</f>
@@ -12474,7 +12462,7 @@
   <sheetData>
     <row r="1" spans="1:18" s="1" customFormat="1" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A1" s="89" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B1" s="89"/>
       <c r="C1" s="89"/>
@@ -12496,10 +12484,10 @@
     </row>
     <row r="3" spans="1:18" ht="23.4" x14ac:dyDescent="0.3">
       <c r="B3" s="48" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G3" s="49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="K3" s="49" t="s">
         <v>86</v>
@@ -12513,7 +12501,7 @@
         <v>81</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E26" s="28" t="s">
         <v>82</v>
@@ -12525,16 +12513,16 @@
         <v>84</v>
       </c>
       <c r="H26" s="28" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I26" s="46" t="s">
         <v>85</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K26" s="46" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L26" s="47" t="s">
         <v>86</v>
@@ -12563,11 +12551,11 @@
       <c r="J27" s="32"/>
       <c r="K27" s="32"/>
       <c r="L27" s="32"/>
-      <c r="N27" s="33" t="s">
+      <c r="N27" s="33">
+        <v>90</v>
+      </c>
+      <c r="O27" s="33" t="s">
         <v>89</v>
-      </c>
-      <c r="O27" s="33" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="28" spans="2:15" ht="18" x14ac:dyDescent="0.35">
@@ -12589,11 +12577,11 @@
       <c r="J28" s="32"/>
       <c r="K28" s="32"/>
       <c r="L28" s="32"/>
-      <c r="N28" s="33" t="s">
-        <v>91</v>
+      <c r="N28" s="33">
+        <v>80</v>
       </c>
       <c r="O28" s="33" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="2:15" ht="18" x14ac:dyDescent="0.35">
@@ -12615,11 +12603,11 @@
       <c r="J29" s="32"/>
       <c r="K29" s="32"/>
       <c r="L29" s="32"/>
-      <c r="N29" s="33" t="s">
-        <v>93</v>
+      <c r="N29" s="33">
+        <v>70</v>
       </c>
       <c r="O29" s="33" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="2:15" ht="18" x14ac:dyDescent="0.35">
@@ -12641,11 +12629,11 @@
       <c r="J30" s="32"/>
       <c r="K30" s="32"/>
       <c r="L30" s="32"/>
-      <c r="N30" s="33" t="s">
-        <v>95</v>
+      <c r="N30" s="33">
+        <v>60</v>
       </c>
       <c r="O30" s="33" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="2:15" ht="18" x14ac:dyDescent="0.35">
@@ -12669,7 +12657,7 @@
       <c r="L31" s="32"/>
       <c r="N31" s="33"/>
       <c r="O31" s="33" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="2:15" ht="18" x14ac:dyDescent="0.35">
@@ -12696,7 +12684,7 @@
     </row>
     <row r="33" spans="2:15" ht="18" x14ac:dyDescent="0.35">
       <c r="B33" s="29" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C33" s="29">
         <v>50</v>
@@ -12714,7 +12702,7 @@
       <c r="K33" s="32"/>
       <c r="L33" s="32"/>
       <c r="N33" s="35" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="O33" s="36">
         <v>0.12</v>
@@ -12722,7 +12710,7 @@
     </row>
     <row r="34" spans="2:15" ht="18" x14ac:dyDescent="0.35">
       <c r="B34" s="29" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C34" s="29">
         <v>87</v>
@@ -12740,7 +12728,7 @@
       <c r="K34" s="32"/>
       <c r="L34" s="32"/>
       <c r="N34" s="37" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O34" s="36">
         <v>0.08</v>
@@ -12748,7 +12736,7 @@
     </row>
     <row r="35" spans="2:15" ht="18" x14ac:dyDescent="0.35">
       <c r="B35" s="29" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C35" s="29">
         <v>6</v>
@@ -12766,7 +12754,7 @@
       <c r="K35" s="32"/>
       <c r="L35" s="32"/>
       <c r="N35" s="37" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="O35" s="36">
         <v>0.05</v>
@@ -12774,7 +12762,7 @@
     </row>
     <row r="36" spans="2:15" ht="18" x14ac:dyDescent="0.35">
       <c r="B36" s="29" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C36" s="29">
         <v>66</v>
@@ -12792,7 +12780,7 @@
       <c r="K36" s="32"/>
       <c r="L36" s="32"/>
       <c r="N36" s="37" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O36" s="36">
         <v>0.03</v>
@@ -12800,7 +12788,7 @@
     </row>
     <row r="37" spans="2:15" ht="18" x14ac:dyDescent="0.35">
       <c r="B37" s="29" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C37" s="29">
         <v>30</v>
@@ -12820,7 +12808,7 @@
     </row>
     <row r="38" spans="2:15" ht="18" x14ac:dyDescent="0.35">
       <c r="B38" s="29" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C38" s="29">
         <v>73</v>
@@ -12840,18 +12828,18 @@
     </row>
     <row r="46" spans="2:15" ht="18" x14ac:dyDescent="0.35">
       <c r="B46" s="38" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48" spans="2:15" ht="18" x14ac:dyDescent="0.3">
       <c r="C48" s="51" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D48" s="51" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E48" s="51" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="3:5" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -12859,10 +12847,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="D49" s="52" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E49" s="52" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50" spans="3:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -12870,10 +12858,10 @@
         <v>#VALUE!</v>
       </c>
       <c r="D50" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="E50" s="52" t="s">
         <v>142</v>
-      </c>
-      <c r="E50" s="52" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="51" spans="3:5" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -12881,10 +12869,10 @@
         <v>#NAME?</v>
       </c>
       <c r="D51" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="E51" s="52" t="s">
         <v>143</v>
-      </c>
-      <c r="E51" s="52" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="52" spans="3:5" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -12892,10 +12880,10 @@
         <v>#REF!</v>
       </c>
       <c r="D52" s="52" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E52" s="52" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="3:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -12903,10 +12891,10 @@
         <v>#N/A</v>
       </c>
       <c r="D53" s="53" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E53" s="52" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="3:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -12914,10 +12902,10 @@
         <v>#NUM!</v>
       </c>
       <c r="D54" s="52" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E54" s="52" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="3:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -12925,10 +12913,10 @@
         <v>#NULL!</v>
       </c>
       <c r="D55" s="53" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E55" s="52" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -12969,7 +12957,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="99" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B1" s="99"/>
       <c r="C1" s="99"/>
@@ -13225,10 +13213,10 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="K16" s="101" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="M16" s="100" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="N16" s="100"/>
       <c r="O16" s="100"/>
@@ -13245,7 +13233,7 @@
     </row>
     <row r="19" spans="2:17" ht="21" x14ac:dyDescent="0.3">
       <c r="B19" s="96" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C19" s="97"/>
       <c r="D19" s="97"/>
@@ -13260,7 +13248,7 @@
       </c>
       <c r="L19" s="6"/>
       <c r="M19" s="93" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="N19" s="93"/>
       <c r="O19" s="93"/>
@@ -13281,7 +13269,7 @@
         <v>5</v>
       </c>
       <c r="M20" s="94" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="N20" s="94"/>
       <c r="O20" s="94"/>
@@ -13299,7 +13287,7 @@
         <v>7</v>
       </c>
       <c r="E21" s="64" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F21" s="27" t="s">
         <v>9</v>
@@ -13318,7 +13306,7 @@
         <v>75</v>
       </c>
       <c r="M21" s="93" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N21" s="93"/>
       <c r="O21" s="93"/>
@@ -13356,7 +13344,7 @@
         <v>74</v>
       </c>
       <c r="M22" s="94" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="N22" s="94"/>
       <c r="O22" s="94"/>
@@ -14128,7 +14116,7 @@
       </c>
       <c r="J44" s="6"/>
       <c r="K44" s="90" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="L44" s="90"/>
       <c r="M44" s="90"/>
@@ -14164,7 +14152,7 @@
       </c>
       <c r="J45" s="6"/>
       <c r="K45" s="91" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="L45" s="91"/>
       <c r="M45" s="91"/>
@@ -14200,7 +14188,7 @@
       </c>
       <c r="J46" s="6"/>
       <c r="K46" s="90" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="L46" s="90"/>
       <c r="M46" s="90"/>
@@ -14223,7 +14211,7 @@
     </row>
     <row r="50" spans="2:17" x14ac:dyDescent="0.3">
       <c r="H50" s="92" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="I50" s="92"/>
       <c r="J50" s="92"/>
@@ -14246,7 +14234,7 @@
         <v>7</v>
       </c>
       <c r="E54" s="64" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F54" s="27" t="s">
         <v>9</v>
@@ -14935,7 +14923,7 @@
       </c>
       <c r="J74" s="6"/>
       <c r="K74" s="90" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="L74" s="90"/>
       <c r="M74" s="90"/>
@@ -14971,7 +14959,7 @@
       </c>
       <c r="J75" s="6"/>
       <c r="K75" s="91" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="L75" s="91"/>
       <c r="M75" s="91"/>
@@ -15007,7 +14995,7 @@
       </c>
       <c r="J76" s="6"/>
       <c r="K76" s="90" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="L76" s="90"/>
       <c r="M76" s="90"/>
@@ -15070,7 +15058,7 @@
       </c>
       <c r="J78" s="6"/>
       <c r="K78" s="90" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="L78" s="90"/>
       <c r="M78" s="90"/>
@@ -15150,7 +15138,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="103" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
@@ -15598,7 +15586,7 @@
     </row>
     <row r="21" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="H21" s="102" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I21" s="102"/>
       <c r="J21" s="102"/>
@@ -15606,7 +15594,7 @@
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="H22" s="102" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I22" s="102"/>
       <c r="J22" s="102"/>
@@ -15614,7 +15602,7 @@
     </row>
     <row r="23" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="H23" s="102" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I23" s="102"/>
       <c r="J23" s="102"/>
@@ -15622,7 +15610,7 @@
     </row>
     <row r="24" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="H24" s="102" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I24" s="102"/>
       <c r="J24" s="102"/>
@@ -15630,7 +15618,7 @@
     </row>
     <row r="28" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E28" s="92" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F28" s="92"/>
       <c r="G28" s="92"/>
@@ -16085,7 +16073,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="79" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
@@ -16132,7 +16120,7 @@
         <v>12</v>
       </c>
       <c r="J3" s="81" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="K3" s="81"/>
       <c r="L3" s="81"/>
@@ -16197,7 +16185,7 @@
         <v>64000</v>
       </c>
       <c r="J5" s="80" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K5" s="80"/>
       <c r="L5" s="80"/>
@@ -16262,10 +16250,10 @@
         <v>71500</v>
       </c>
       <c r="J7" s="65" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="L7" s="73" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="M7" s="74"/>
       <c r="N7" s="74"/>
@@ -16328,10 +16316,10 @@
         <v>80690</v>
       </c>
       <c r="J9" s="65" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L9" s="74" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="M9" s="74"/>
       <c r="N9" s="74"/>
@@ -16394,10 +16382,10 @@
         <v>89028</v>
       </c>
       <c r="J11" s="65" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="L11" s="73" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="M11" s="74"/>
       <c r="N11" s="74"/>
@@ -16460,10 +16448,10 @@
         <v>65500</v>
       </c>
       <c r="J13" s="65" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L13" s="73" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="M13" s="74"/>
       <c r="N13" s="74"/>
@@ -16526,10 +16514,10 @@
         <v>92004</v>
       </c>
       <c r="J15" s="65" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="L15" s="73" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="M15" s="74"/>
       <c r="N15" s="74"/>
@@ -16592,10 +16580,10 @@
         <v>120000</v>
       </c>
       <c r="J17" s="65" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="L17" s="73" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M17" s="74"/>
       <c r="N17" s="74"/>
@@ -16955,7 +16943,7 @@
     </row>
     <row r="33" spans="1:18" ht="23.4" x14ac:dyDescent="0.3">
       <c r="H33" s="86" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I33" s="86"/>
       <c r="J33" s="86"/>
@@ -16987,7 +16975,7 @@
         <v>12</v>
       </c>
       <c r="J35" s="81" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="K35" s="81"/>
       <c r="L35" s="81"/>
@@ -17052,7 +17040,7 @@
         <v>64000</v>
       </c>
       <c r="J37" s="80" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K37" s="80"/>
       <c r="L37" s="80"/>
@@ -17117,10 +17105,10 @@
         <v>71500</v>
       </c>
       <c r="J39" s="65" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="L39" s="73" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="M39" s="74"/>
       <c r="N39" s="74"/>
@@ -17183,10 +17171,10 @@
         <v>80690</v>
       </c>
       <c r="J41" s="65" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L41" s="74" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="M41" s="74"/>
       <c r="N41" s="74"/>
@@ -17249,10 +17237,10 @@
         <v>89028</v>
       </c>
       <c r="J43" s="65" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="L43" s="73" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="M43" s="74"/>
       <c r="N43" s="74"/>
@@ -17315,10 +17303,10 @@
         <v>65500</v>
       </c>
       <c r="J45" s="65" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L45" s="73" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="M45" s="74"/>
       <c r="N45" s="74"/>
@@ -17381,10 +17369,10 @@
         <v>92004</v>
       </c>
       <c r="J47" s="65" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="L47" s="73" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="M47" s="74"/>
       <c r="N47" s="74"/>
@@ -17447,10 +17435,10 @@
         <v>120000</v>
       </c>
       <c r="J49" s="65" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="L49" s="73" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M49" s="74"/>
       <c r="N49" s="74"/>
@@ -17775,7 +17763,7 @@
         <v>83000</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="K59" s="66" t="str">
         <f t="shared" si="3"/>
@@ -17810,11 +17798,11 @@
     </row>
     <row r="66" spans="10:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J66" s="82" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K66" s="83"/>
       <c r="M66" s="77" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="N66" s="78"/>
     </row>
@@ -17824,19 +17812,19 @@
     </row>
     <row r="68" spans="10:14" ht="18" x14ac:dyDescent="0.3">
       <c r="M68" s="77" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="N68" s="78"/>
     </row>
     <row r="70" spans="10:14" ht="18" x14ac:dyDescent="0.3">
       <c r="M70" s="77" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="N70" s="78"/>
     </row>
     <row r="72" spans="10:14" ht="18" x14ac:dyDescent="0.3">
       <c r="M72" s="77" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N72" s="78"/>
     </row>
@@ -17894,7 +17882,7 @@
     </row>
     <row r="5" spans="4:5" ht="18" x14ac:dyDescent="0.35">
       <c r="D5" s="68" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E5" s="70">
         <f>ROUND(E2,2)</f>
@@ -17903,7 +17891,7 @@
     </row>
     <row r="6" spans="4:5" ht="18" x14ac:dyDescent="0.35">
       <c r="D6" s="68" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E6" s="70">
         <f>ROUNDUP(E2,1)</f>
@@ -17912,7 +17900,7 @@
     </row>
     <row r="7" spans="4:5" ht="18" x14ac:dyDescent="0.35">
       <c r="D7" s="68" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E7" s="70">
         <f>ROUNDDOWN(E2,3)</f>
@@ -17991,7 +17979,7 @@
     <row r="4" spans="1:24" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="67"/>
       <c r="C4" s="104" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D4" s="104"/>
       <c r="E4" s="104"/>
@@ -18016,7 +18004,7 @@
     <row r="7" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="67"/>
       <c r="C7" s="106" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D7" s="106"/>
       <c r="E7" s="106"/>
@@ -18037,7 +18025,7 @@
     <row r="9" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="67"/>
       <c r="C9" s="106" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D9" s="106"/>
       <c r="E9" s="106"/>
@@ -18058,7 +18046,7 @@
     <row r="11" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="67"/>
       <c r="C11" s="106" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D11" s="106"/>
       <c r="E11" s="106"/>
@@ -18095,7 +18083,7 @@
     <row r="17" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="67"/>
       <c r="F17" s="105" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G17" s="105"/>
       <c r="H17" s="105"/>

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D256A4F0-966D-49F4-A4A3-D3FBAAE48A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66260A10-B8AB-4E3B-B632-6EDD0376A069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,6 +56,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12311,7 +12333,7 @@
       </c>
       <c r="D9" s="40">
         <f ca="1">NOW()</f>
-        <v>46294.100298148151</v>
+        <v>46294.103674999998</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="18" x14ac:dyDescent="0.35">
@@ -12544,7 +12566,10 @@
         <f>IF(C27&gt;80, "Passed", "Failed")</f>
         <v>Failed</v>
       </c>
-      <c r="F27" s="32"/>
+      <c r="F27" s="32" t="str" cm="1">
+        <f t="array" ref="F27">_xlfn.IFS(C27&gt;=$N$27,"Excellent",C27&gt;=$N$28, "Very Good", C27&gt;=$N$29, "Good", C27&gt;=$N$30, "Passed", C27&lt;$N$30, "Failed")</f>
+        <v>Passed</v>
+      </c>
       <c r="G27" s="50"/>
       <c r="H27" s="32"/>
       <c r="I27" s="32"/>
@@ -12570,7 +12595,10 @@
         <f t="shared" ref="E28:E38" si="0">IF(C28&gt;80, "Passed", "Failed")</f>
         <v>Passed</v>
       </c>
-      <c r="F28" s="32"/>
+      <c r="F28" s="32" t="str" cm="1">
+        <f t="array" ref="F28">_xlfn.IFS(C28&gt;=$N$27,"Excellent",C28&gt;=$N$28, "Very Good", C28&gt;=$N$29, "Good", C28&gt;=$N$30, "Passed", C28&lt;$N$30, "Failed")</f>
+        <v>Very Good</v>
+      </c>
       <c r="G28" s="50"/>
       <c r="H28" s="32"/>
       <c r="I28" s="32"/>
@@ -12596,7 +12624,10 @@
         <f t="shared" si="0"/>
         <v>Failed</v>
       </c>
-      <c r="F29" s="32"/>
+      <c r="F29" s="32" t="str" cm="1">
+        <f t="array" ref="F29">_xlfn.IFS(C29&gt;=$N$27,"Excellent",C29&gt;=$N$28, "Very Good", C29&gt;=$N$29, "Good", C29&gt;=$N$30, "Passed", C29&lt;$N$30, "Failed")</f>
+        <v>Failed</v>
+      </c>
       <c r="G29" s="50"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
@@ -12622,7 +12653,10 @@
         <f t="shared" si="0"/>
         <v>Failed</v>
       </c>
-      <c r="F30" s="32"/>
+      <c r="F30" s="32" t="str" cm="1">
+        <f t="array" ref="F30">_xlfn.IFS(C30&gt;=$N$27,"Excellent",C30&gt;=$N$28, "Very Good", C30&gt;=$N$29, "Good", C30&gt;=$N$30, "Passed", C30&lt;$N$30, "Failed")</f>
+        <v>Good</v>
+      </c>
       <c r="G30" s="50"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
@@ -12648,7 +12682,10 @@
         <f t="shared" si="0"/>
         <v>Failed</v>
       </c>
-      <c r="F31" s="32"/>
+      <c r="F31" s="32" t="str" cm="1">
+        <f t="array" ref="F31">_xlfn.IFS(C31&gt;=$N$27,"Excellent",C31&gt;=$N$28, "Very Good", C31&gt;=$N$29, "Good", C31&gt;=$N$30, "Passed", C31&lt;$N$30, "Failed")</f>
+        <v>Passed</v>
+      </c>
       <c r="G31" s="50"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
@@ -12672,7 +12709,10 @@
         <f t="shared" si="0"/>
         <v>Passed</v>
       </c>
-      <c r="F32" s="32"/>
+      <c r="F32" s="32" t="str" cm="1">
+        <f t="array" ref="F32">_xlfn.IFS(C32&gt;=$N$27,"Excellent",C32&gt;=$N$28, "Very Good", C32&gt;=$N$29, "Good", C32&gt;=$N$30, "Passed", C32&lt;$N$30, "Failed")</f>
+        <v>Excellent</v>
+      </c>
       <c r="G32" s="50"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
@@ -12694,7 +12734,10 @@
         <f t="shared" si="0"/>
         <v>Failed</v>
       </c>
-      <c r="F33" s="32"/>
+      <c r="F33" s="32" t="str" cm="1">
+        <f t="array" ref="F33">_xlfn.IFS(C33&gt;=$N$27,"Excellent",C33&gt;=$N$28, "Very Good", C33&gt;=$N$29, "Good", C33&gt;=$N$30, "Passed", C33&lt;$N$30, "Failed")</f>
+        <v>Failed</v>
+      </c>
       <c r="G33" s="50"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
@@ -12720,7 +12763,10 @@
         <f t="shared" si="0"/>
         <v>Passed</v>
       </c>
-      <c r="F34" s="32"/>
+      <c r="F34" s="32" t="str" cm="1">
+        <f t="array" ref="F34">_xlfn.IFS(C34&gt;=$N$27,"Excellent",C34&gt;=$N$28, "Very Good", C34&gt;=$N$29, "Good", C34&gt;=$N$30, "Passed", C34&lt;$N$30, "Failed")</f>
+        <v>Very Good</v>
+      </c>
       <c r="G34" s="50"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
@@ -12746,7 +12792,10 @@
         <f t="shared" si="0"/>
         <v>Failed</v>
       </c>
-      <c r="F35" s="32"/>
+      <c r="F35" s="32" t="str" cm="1">
+        <f t="array" ref="F35">_xlfn.IFS(C35&gt;=$N$27,"Excellent",C35&gt;=$N$28, "Very Good", C35&gt;=$N$29, "Good", C35&gt;=$N$30, "Passed", C35&lt;$N$30, "Failed")</f>
+        <v>Failed</v>
+      </c>
       <c r="G35" s="50"/>
       <c r="H35" s="32"/>
       <c r="I35" s="32"/>
@@ -12772,7 +12821,10 @@
         <f t="shared" si="0"/>
         <v>Failed</v>
       </c>
-      <c r="F36" s="32"/>
+      <c r="F36" s="32" t="str" cm="1">
+        <f t="array" ref="F36">_xlfn.IFS(C36&gt;=$N$27,"Excellent",C36&gt;=$N$28, "Very Good", C36&gt;=$N$29, "Good", C36&gt;=$N$30, "Passed", C36&lt;$N$30, "Failed")</f>
+        <v>Passed</v>
+      </c>
       <c r="G36" s="50"/>
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
@@ -12798,7 +12850,10 @@
         <f t="shared" si="0"/>
         <v>Failed</v>
       </c>
-      <c r="F37" s="32"/>
+      <c r="F37" s="32" t="str" cm="1">
+        <f t="array" ref="F37">_xlfn.IFS(C37&gt;=$N$27,"Excellent",C37&gt;=$N$28, "Very Good", C37&gt;=$N$29, "Good", C37&gt;=$N$30, "Passed", C37&lt;$N$30, "Failed")</f>
+        <v>Failed</v>
+      </c>
       <c r="G37" s="50"/>
       <c r="H37" s="32"/>
       <c r="I37" s="32"/>
@@ -12818,7 +12873,10 @@
         <f t="shared" si="0"/>
         <v>Failed</v>
       </c>
-      <c r="F38" s="32"/>
+      <c r="F38" s="32" t="str" cm="1">
+        <f t="array" ref="F38">_xlfn.IFS(C38&gt;=$N$27,"Excellent",C38&gt;=$N$28, "Very Good", C38&gt;=$N$29, "Good", C38&gt;=$N$30, "Passed", C38&lt;$N$30, "Failed")</f>
+        <v>Good</v>
+      </c>
       <c r="G38" s="50"/>
       <c r="H38" s="32"/>
       <c r="I38" s="32"/>

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66260A10-B8AB-4E3B-B632-6EDD0376A069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6D5F04-8DF6-4117-8D1E-2680E8461564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1780,8 +1780,8 @@
       <xdr:rowOff>144780</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>470535</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>280035</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
@@ -1841,8 +1841,8 @@
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
@@ -12333,7 +12333,7 @@
       </c>
       <c r="D9" s="40">
         <f ca="1">NOW()</f>
-        <v>46294.103674999998</v>
+        <v>46294.107998842592</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="18" x14ac:dyDescent="0.35">
@@ -12471,14 +12471,14 @@
     <col min="2" max="2" width="21.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.44140625" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" customWidth="1"/>
+    <col min="5" max="5" width="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.109375" customWidth="1"/>
-    <col min="11" max="11" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="11.21875" customWidth="1"/>
+    <col min="11" max="11" width="17.21875" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" customWidth="1"/>
     <col min="13" max="13" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12570,8 +12570,14 @@
         <f t="array" ref="F27">_xlfn.IFS(C27&gt;=$N$27,"Excellent",C27&gt;=$N$28, "Very Good", C27&gt;=$N$29, "Good", C27&gt;=$N$30, "Passed", C27&lt;$N$30, "Failed")</f>
         <v>Passed</v>
       </c>
-      <c r="G27" s="50"/>
-      <c r="H27" s="32"/>
+      <c r="G27" s="50" t="str" cm="1">
+        <f t="array" ref="G27">IFERROR(_xlfn.IFS(C27&gt;=$N$27,"Excellent",C27&gt;=$N$28, "Very Good", C27&gt;=$N$29, "Good", C27&gt;=$N$30, "Passed", C27&lt;$N$30, "Failed"),"Error")</f>
+        <v>Passed</v>
+      </c>
+      <c r="H27" s="32" t="str" cm="1">
+        <f t="array" ref="H27">_xlfn.IFNA(_xlfn.IFS(C27&gt;=$N$27,"Excellent",C27&gt;=$N$28, "Very Good", C27&gt;=$N$29, "Good", C27&gt;=$N$30, "Passed", C27&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <v>Passed</v>
+      </c>
       <c r="I27" s="32"/>
       <c r="J27" s="32"/>
       <c r="K27" s="32"/>
@@ -12599,8 +12605,14 @@
         <f t="array" ref="F28">_xlfn.IFS(C28&gt;=$N$27,"Excellent",C28&gt;=$N$28, "Very Good", C28&gt;=$N$29, "Good", C28&gt;=$N$30, "Passed", C28&lt;$N$30, "Failed")</f>
         <v>Very Good</v>
       </c>
-      <c r="G28" s="50"/>
-      <c r="H28" s="32"/>
+      <c r="G28" s="50" t="str" cm="1">
+        <f t="array" ref="G28">IFERROR(_xlfn.IFS(C28&gt;=$N$27,"Excellent",C28&gt;=$N$28, "Very Good", C28&gt;=$N$29, "Good", C28&gt;=$N$30, "Passed", C28&lt;$N$30, "Failed"),"Error")</f>
+        <v>Very Good</v>
+      </c>
+      <c r="H28" s="32" t="str" cm="1">
+        <f t="array" ref="H28">_xlfn.IFNA(_xlfn.IFS(C28&gt;=$N$27,"Excellent",C28&gt;=$N$28, "Very Good", C28&gt;=$N$29, "Good", C28&gt;=$N$30, "Passed", C28&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <v>Very Good</v>
+      </c>
       <c r="I28" s="32"/>
       <c r="J28" s="32"/>
       <c r="K28" s="32"/>
@@ -12628,8 +12640,14 @@
         <f t="array" ref="F29">_xlfn.IFS(C29&gt;=$N$27,"Excellent",C29&gt;=$N$28, "Very Good", C29&gt;=$N$29, "Good", C29&gt;=$N$30, "Passed", C29&lt;$N$30, "Failed")</f>
         <v>Failed</v>
       </c>
-      <c r="G29" s="50"/>
-      <c r="H29" s="32"/>
+      <c r="G29" s="50" t="str" cm="1">
+        <f t="array" ref="G29">IFERROR(_xlfn.IFS(C29&gt;=$N$27,"Excellent",C29&gt;=$N$28, "Very Good", C29&gt;=$N$29, "Good", C29&gt;=$N$30, "Passed", C29&lt;$N$30, "Failed"),"Error")</f>
+        <v>Failed</v>
+      </c>
+      <c r="H29" s="32" t="str" cm="1">
+        <f t="array" ref="H29">_xlfn.IFNA(_xlfn.IFS(C29&gt;=$N$27,"Excellent",C29&gt;=$N$28, "Very Good", C29&gt;=$N$29, "Good", C29&gt;=$N$30, "Passed", C29&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <v>Failed</v>
+      </c>
       <c r="I29" s="32"/>
       <c r="J29" s="32"/>
       <c r="K29" s="32"/>
@@ -12657,8 +12675,14 @@
         <f t="array" ref="F30">_xlfn.IFS(C30&gt;=$N$27,"Excellent",C30&gt;=$N$28, "Very Good", C30&gt;=$N$29, "Good", C30&gt;=$N$30, "Passed", C30&lt;$N$30, "Failed")</f>
         <v>Good</v>
       </c>
-      <c r="G30" s="50"/>
-      <c r="H30" s="32"/>
+      <c r="G30" s="50" t="str" cm="1">
+        <f t="array" ref="G30">IFERROR(_xlfn.IFS(C30&gt;=$N$27,"Excellent",C30&gt;=$N$28, "Very Good", C30&gt;=$N$29, "Good", C30&gt;=$N$30, "Passed", C30&lt;$N$30, "Failed"),"Error")</f>
+        <v>Good</v>
+      </c>
+      <c r="H30" s="32" t="str" cm="1">
+        <f t="array" ref="H30">_xlfn.IFNA(_xlfn.IFS(C30&gt;=$N$27,"Excellent",C30&gt;=$N$28, "Very Good", C30&gt;=$N$29, "Good", C30&gt;=$N$30, "Passed", C30&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <v>Good</v>
+      </c>
       <c r="I30" s="32"/>
       <c r="J30" s="32"/>
       <c r="K30" s="32"/>
@@ -12686,8 +12710,14 @@
         <f t="array" ref="F31">_xlfn.IFS(C31&gt;=$N$27,"Excellent",C31&gt;=$N$28, "Very Good", C31&gt;=$N$29, "Good", C31&gt;=$N$30, "Passed", C31&lt;$N$30, "Failed")</f>
         <v>Passed</v>
       </c>
-      <c r="G31" s="50"/>
-      <c r="H31" s="32"/>
+      <c r="G31" s="50" t="str" cm="1">
+        <f t="array" ref="G31">IFERROR(_xlfn.IFS(C31&gt;=$N$27,"Excellent",C31&gt;=$N$28, "Very Good", C31&gt;=$N$29, "Good", C31&gt;=$N$30, "Passed", C31&lt;$N$30, "Failed"),"Error")</f>
+        <v>Passed</v>
+      </c>
+      <c r="H31" s="32" t="str" cm="1">
+        <f t="array" ref="H31">_xlfn.IFNA(_xlfn.IFS(C31&gt;=$N$27,"Excellent",C31&gt;=$N$28, "Very Good", C31&gt;=$N$29, "Good", C31&gt;=$N$30, "Passed", C31&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <v>Passed</v>
+      </c>
       <c r="I31" s="32"/>
       <c r="J31" s="32"/>
       <c r="K31" s="32"/>
@@ -12713,8 +12743,14 @@
         <f t="array" ref="F32">_xlfn.IFS(C32&gt;=$N$27,"Excellent",C32&gt;=$N$28, "Very Good", C32&gt;=$N$29, "Good", C32&gt;=$N$30, "Passed", C32&lt;$N$30, "Failed")</f>
         <v>Excellent</v>
       </c>
-      <c r="G32" s="50"/>
-      <c r="H32" s="32"/>
+      <c r="G32" s="50" t="str" cm="1">
+        <f t="array" ref="G32">IFERROR(_xlfn.IFS(C32&gt;=$N$27,"Excellent",C32&gt;=$N$28, "Very Good", C32&gt;=$N$29, "Good", C32&gt;=$N$30, "Passed", C32&lt;$N$30, "Failed"),"Error")</f>
+        <v>Excellent</v>
+      </c>
+      <c r="H32" s="32" t="str" cm="1">
+        <f t="array" ref="H32">_xlfn.IFNA(_xlfn.IFS(C32&gt;=$N$27,"Excellent",C32&gt;=$N$28, "Very Good", C32&gt;=$N$29, "Good", C32&gt;=$N$30, "Passed", C32&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <v>Excellent</v>
+      </c>
       <c r="I32" s="32"/>
       <c r="J32" s="32"/>
       <c r="K32" s="32"/>
@@ -12738,8 +12774,14 @@
         <f t="array" ref="F33">_xlfn.IFS(C33&gt;=$N$27,"Excellent",C33&gt;=$N$28, "Very Good", C33&gt;=$N$29, "Good", C33&gt;=$N$30, "Passed", C33&lt;$N$30, "Failed")</f>
         <v>Failed</v>
       </c>
-      <c r="G33" s="50"/>
-      <c r="H33" s="32"/>
+      <c r="G33" s="50" t="str" cm="1">
+        <f t="array" ref="G33">IFERROR(_xlfn.IFS(C33&gt;=$N$27,"Excellent",C33&gt;=$N$28, "Very Good", C33&gt;=$N$29, "Good", C33&gt;=$N$30, "Passed", C33&lt;$N$30, "Failed"),"Error")</f>
+        <v>Failed</v>
+      </c>
+      <c r="H33" s="32" t="str" cm="1">
+        <f t="array" ref="H33">_xlfn.IFNA(_xlfn.IFS(C33&gt;=$N$27,"Excellent",C33&gt;=$N$28, "Very Good", C33&gt;=$N$29, "Good", C33&gt;=$N$30, "Passed", C33&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <v>Failed</v>
+      </c>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>
       <c r="K33" s="32"/>
@@ -12767,8 +12809,14 @@
         <f t="array" ref="F34">_xlfn.IFS(C34&gt;=$N$27,"Excellent",C34&gt;=$N$28, "Very Good", C34&gt;=$N$29, "Good", C34&gt;=$N$30, "Passed", C34&lt;$N$30, "Failed")</f>
         <v>Very Good</v>
       </c>
-      <c r="G34" s="50"/>
-      <c r="H34" s="32"/>
+      <c r="G34" s="50" t="str" cm="1">
+        <f t="array" ref="G34">IFERROR(_xlfn.IFS(C34&gt;=$N$27,"Excellent",C34&gt;=$N$28, "Very Good", C34&gt;=$N$29, "Good", C34&gt;=$N$30, "Passed", C34&lt;$N$30, "Failed"),"Error")</f>
+        <v>Very Good</v>
+      </c>
+      <c r="H34" s="32" t="str" cm="1">
+        <f t="array" ref="H34">_xlfn.IFNA(_xlfn.IFS(C34&gt;=$N$27,"Excellent",C34&gt;=$N$28, "Very Good", C34&gt;=$N$29, "Good", C34&gt;=$N$30, "Passed", C34&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <v>Very Good</v>
+      </c>
       <c r="I34" s="32"/>
       <c r="J34" s="32"/>
       <c r="K34" s="32"/>
@@ -12796,8 +12844,14 @@
         <f t="array" ref="F35">_xlfn.IFS(C35&gt;=$N$27,"Excellent",C35&gt;=$N$28, "Very Good", C35&gt;=$N$29, "Good", C35&gt;=$N$30, "Passed", C35&lt;$N$30, "Failed")</f>
         <v>Failed</v>
       </c>
-      <c r="G35" s="50"/>
-      <c r="H35" s="32"/>
+      <c r="G35" s="50" t="str" cm="1">
+        <f t="array" ref="G35">IFERROR(_xlfn.IFS(C35&gt;=$N$27,"Excellent",C35&gt;=$N$28, "Very Good", C35&gt;=$N$29, "Good", C35&gt;=$N$30, "Passed", C35&lt;$N$30, "Failed"),"Error")</f>
+        <v>Failed</v>
+      </c>
+      <c r="H35" s="32" t="str" cm="1">
+        <f t="array" ref="H35">_xlfn.IFNA(_xlfn.IFS(C35&gt;=$N$27,"Excellent",C35&gt;=$N$28, "Very Good", C35&gt;=$N$29, "Good", C35&gt;=$N$30, "Passed", C35&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <v>Failed</v>
+      </c>
       <c r="I35" s="32"/>
       <c r="J35" s="32"/>
       <c r="K35" s="32"/>
@@ -12825,8 +12879,14 @@
         <f t="array" ref="F36">_xlfn.IFS(C36&gt;=$N$27,"Excellent",C36&gt;=$N$28, "Very Good", C36&gt;=$N$29, "Good", C36&gt;=$N$30, "Passed", C36&lt;$N$30, "Failed")</f>
         <v>Passed</v>
       </c>
-      <c r="G36" s="50"/>
-      <c r="H36" s="32"/>
+      <c r="G36" s="50" t="str" cm="1">
+        <f t="array" ref="G36">IFERROR(_xlfn.IFS(C36&gt;=$N$27,"Excellent",C36&gt;=$N$28, "Very Good", C36&gt;=$N$29, "Good", C36&gt;=$N$30, "Passed", C36&lt;$N$30, "Failed"),"Error")</f>
+        <v>Passed</v>
+      </c>
+      <c r="H36" s="32" t="str" cm="1">
+        <f t="array" ref="H36">_xlfn.IFNA(_xlfn.IFS(C36&gt;=$N$27,"Excellent",C36&gt;=$N$28, "Very Good", C36&gt;=$N$29, "Good", C36&gt;=$N$30, "Passed", C36&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <v>Passed</v>
+      </c>
       <c r="I36" s="32"/>
       <c r="J36" s="32"/>
       <c r="K36" s="32"/>
@@ -12854,8 +12914,14 @@
         <f t="array" ref="F37">_xlfn.IFS(C37&gt;=$N$27,"Excellent",C37&gt;=$N$28, "Very Good", C37&gt;=$N$29, "Good", C37&gt;=$N$30, "Passed", C37&lt;$N$30, "Failed")</f>
         <v>Failed</v>
       </c>
-      <c r="G37" s="50"/>
-      <c r="H37" s="32"/>
+      <c r="G37" s="50" t="str" cm="1">
+        <f t="array" ref="G37">IFERROR(_xlfn.IFS(C37&gt;=$N$27,"Excellent",C37&gt;=$N$28, "Very Good", C37&gt;=$N$29, "Good", C37&gt;=$N$30, "Passed", C37&lt;$N$30, "Failed"),"Error")</f>
+        <v>Failed</v>
+      </c>
+      <c r="H37" s="32" t="str" cm="1">
+        <f t="array" ref="H37">_xlfn.IFNA(_xlfn.IFS(C37&gt;=$N$27,"Excellent",C37&gt;=$N$28, "Very Good", C37&gt;=$N$29, "Good", C37&gt;=$N$30, "Passed", C37&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <v>Failed</v>
+      </c>
       <c r="I37" s="32"/>
       <c r="J37" s="32"/>
       <c r="K37" s="32"/>
@@ -12877,8 +12943,14 @@
         <f t="array" ref="F38">_xlfn.IFS(C38&gt;=$N$27,"Excellent",C38&gt;=$N$28, "Very Good", C38&gt;=$N$29, "Good", C38&gt;=$N$30, "Passed", C38&lt;$N$30, "Failed")</f>
         <v>Good</v>
       </c>
-      <c r="G38" s="50"/>
-      <c r="H38" s="32"/>
+      <c r="G38" s="50" t="str" cm="1">
+        <f t="array" ref="G38">IFERROR(_xlfn.IFS(C38&gt;=$N$27,"Excellent",C38&gt;=$N$28, "Very Good", C38&gt;=$N$29, "Good", C38&gt;=$N$30, "Passed", C38&lt;$N$30, "Failed"),"Error")</f>
+        <v>Good</v>
+      </c>
+      <c r="H38" s="32" t="str" cm="1">
+        <f t="array" ref="H38">_xlfn.IFNA(_xlfn.IFS(C38&gt;=$N$27,"Excellent",C38&gt;=$N$28, "Very Good", C38&gt;=$N$29, "Good", C38&gt;=$N$30, "Passed", C38&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <v>Good</v>
+      </c>
       <c r="I38" s="32"/>
       <c r="J38" s="32"/>
       <c r="K38" s="32"/>

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6D5F04-8DF6-4117-8D1E-2680E8461564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA37B55-97C0-4073-BDE2-AADE5A25E368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="206">
   <si>
     <t>id</t>
   </si>
@@ -753,6 +753,9 @@
   </si>
   <si>
     <t xml:space="preserve">Xlookup </t>
+  </si>
+  <si>
+    <t>if(and)</t>
   </si>
 </sst>
 </file>
@@ -1841,8 +1844,8 @@
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1123950</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
@@ -12333,7 +12336,7 @@
       </c>
       <c r="D9" s="40">
         <f ca="1">NOW()</f>
-        <v>46294.107998842592</v>
+        <v>46294.112390509261</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="18" x14ac:dyDescent="0.35">
@@ -12474,7 +12477,7 @@
     <col min="5" max="5" width="26" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="11.21875" customWidth="1"/>
     <col min="11" max="11" width="17.21875" customWidth="1"/>
@@ -12515,7 +12518,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B26" s="27" t="s">
         <v>80</v>
       </c>
@@ -12546,15 +12549,18 @@
       <c r="K26" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="L26" s="47" t="s">
+      <c r="L26" s="46" t="s">
+        <v>205</v>
+      </c>
+      <c r="M26" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="N26" s="87" t="s">
+      <c r="O26" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="O26" s="88"/>
-    </row>
-    <row r="27" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="P26" s="88"/>
+    </row>
+    <row r="27" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
         <v>88</v>
       </c>
@@ -12567,29 +12573,39 @@
         <v>Failed</v>
       </c>
       <c r="F27" s="32" t="str" cm="1">
-        <f t="array" ref="F27">_xlfn.IFS(C27&gt;=$N$27,"Excellent",C27&gt;=$N$28, "Very Good", C27&gt;=$N$29, "Good", C27&gt;=$N$30, "Passed", C27&lt;$N$30, "Failed")</f>
+        <f t="array" ref="F27">_xlfn.IFS(C27&gt;=$O$27,"Excellent",C27&gt;=$O$28, "Very Good", C27&gt;=$O$29, "Good", C27&gt;=$O$30, "Passed", C27&lt;$O$30, "Failed")</f>
         <v>Passed</v>
       </c>
       <c r="G27" s="50" t="str" cm="1">
-        <f t="array" ref="G27">IFERROR(_xlfn.IFS(C27&gt;=$N$27,"Excellent",C27&gt;=$N$28, "Very Good", C27&gt;=$N$29, "Good", C27&gt;=$N$30, "Passed", C27&lt;$N$30, "Failed"),"Error")</f>
+        <f t="array" ref="G27">IFERROR(_xlfn.IFS(C27&gt;=$O$27,"Excellent",C27&gt;=$O$28, "Very Good", C27&gt;=$O$29, "Good", C27&gt;=$O$30, "Passed", C27&lt;$O$30, "Failed"),"Error")</f>
         <v>Passed</v>
       </c>
       <c r="H27" s="32" t="str" cm="1">
-        <f t="array" ref="H27">_xlfn.IFNA(_xlfn.IFS(C27&gt;=$N$27,"Excellent",C27&gt;=$N$28, "Very Good", C27&gt;=$N$29, "Good", C27&gt;=$N$30, "Passed", C27&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <f t="array" ref="H27">_xlfn.IFNA(_xlfn.IFS(C27&gt;=$O$27,"Excellent",C27&gt;=$O$28, "Very Good", C27&gt;=$O$29, "Good", C27&gt;=$O$30, "Passed", C27&lt;$O$30, "Failed"), _xleta.N/A)</f>
         <v>Passed</v>
       </c>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
+      <c r="I27" s="32" t="b">
+        <f>AND(C27&gt;50, C28&gt;60)</f>
+        <v>1</v>
+      </c>
+      <c r="J27" s="32" t="b">
+        <f>OR(C27&gt;70, C28&gt;60)</f>
+        <v>1</v>
+      </c>
+      <c r="K27" s="32" t="b">
+        <f>NOT(J27)</f>
+        <v>0</v>
+      </c>
       <c r="L27" s="32"/>
-      <c r="N27" s="33">
+      <c r="M27" s="32"/>
+      <c r="O27" s="33">
         <v>90</v>
       </c>
-      <c r="O27" s="33" t="s">
+      <c r="P27" s="33" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B28" s="29" t="s">
         <v>38</v>
       </c>
@@ -12602,29 +12618,39 @@
         <v>Passed</v>
       </c>
       <c r="F28" s="32" t="str" cm="1">
-        <f t="array" ref="F28">_xlfn.IFS(C28&gt;=$N$27,"Excellent",C28&gt;=$N$28, "Very Good", C28&gt;=$N$29, "Good", C28&gt;=$N$30, "Passed", C28&lt;$N$30, "Failed")</f>
+        <f t="array" ref="F28">_xlfn.IFS(C28&gt;=$O$27,"Excellent",C28&gt;=$O$28, "Very Good", C28&gt;=$O$29, "Good", C28&gt;=$O$30, "Passed", C28&lt;$O$30, "Failed")</f>
         <v>Very Good</v>
       </c>
       <c r="G28" s="50" t="str" cm="1">
-        <f t="array" ref="G28">IFERROR(_xlfn.IFS(C28&gt;=$N$27,"Excellent",C28&gt;=$N$28, "Very Good", C28&gt;=$N$29, "Good", C28&gt;=$N$30, "Passed", C28&lt;$N$30, "Failed"),"Error")</f>
+        <f t="array" ref="G28">IFERROR(_xlfn.IFS(C28&gt;=$O$27,"Excellent",C28&gt;=$O$28, "Very Good", C28&gt;=$O$29, "Good", C28&gt;=$O$30, "Passed", C28&lt;$O$30, "Failed"),"Error")</f>
         <v>Very Good</v>
       </c>
       <c r="H28" s="32" t="str" cm="1">
-        <f t="array" ref="H28">_xlfn.IFNA(_xlfn.IFS(C28&gt;=$N$27,"Excellent",C28&gt;=$N$28, "Very Good", C28&gt;=$N$29, "Good", C28&gt;=$N$30, "Passed", C28&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <f t="array" ref="H28">_xlfn.IFNA(_xlfn.IFS(C28&gt;=$O$27,"Excellent",C28&gt;=$O$28, "Very Good", C28&gt;=$O$29, "Good", C28&gt;=$O$30, "Passed", C28&lt;$O$30, "Failed"), _xleta.N/A)</f>
         <v>Very Good</v>
       </c>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
+      <c r="I28" s="32" t="b">
+        <f>AND(C28&gt;50, C29&gt;60)</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="32" t="b">
+        <f t="shared" ref="J28:J38" si="1">OR(C28&gt;70, C29&gt;60)</f>
+        <v>1</v>
+      </c>
+      <c r="K28" s="32" t="b">
+        <f t="shared" ref="K28:K38" si="2">NOT(J28)</f>
+        <v>0</v>
+      </c>
       <c r="L28" s="32"/>
-      <c r="N28" s="33">
+      <c r="M28" s="32"/>
+      <c r="O28" s="33">
         <v>80</v>
       </c>
-      <c r="O28" s="33" t="s">
+      <c r="P28" s="33" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B29" s="29" t="s">
         <v>57</v>
       </c>
@@ -12637,29 +12663,39 @@
         <v>Failed</v>
       </c>
       <c r="F29" s="32" t="str" cm="1">
-        <f t="array" ref="F29">_xlfn.IFS(C29&gt;=$N$27,"Excellent",C29&gt;=$N$28, "Very Good", C29&gt;=$N$29, "Good", C29&gt;=$N$30, "Passed", C29&lt;$N$30, "Failed")</f>
+        <f t="array" ref="F29">_xlfn.IFS(C29&gt;=$O$27,"Excellent",C29&gt;=$O$28, "Very Good", C29&gt;=$O$29, "Good", C29&gt;=$O$30, "Passed", C29&lt;$O$30, "Failed")</f>
         <v>Failed</v>
       </c>
       <c r="G29" s="50" t="str" cm="1">
-        <f t="array" ref="G29">IFERROR(_xlfn.IFS(C29&gt;=$N$27,"Excellent",C29&gt;=$N$28, "Very Good", C29&gt;=$N$29, "Good", C29&gt;=$N$30, "Passed", C29&lt;$N$30, "Failed"),"Error")</f>
+        <f t="array" ref="G29">IFERROR(_xlfn.IFS(C29&gt;=$O$27,"Excellent",C29&gt;=$O$28, "Very Good", C29&gt;=$O$29, "Good", C29&gt;=$O$30, "Passed", C29&lt;$O$30, "Failed"),"Error")</f>
         <v>Failed</v>
       </c>
       <c r="H29" s="32" t="str" cm="1">
-        <f t="array" ref="H29">_xlfn.IFNA(_xlfn.IFS(C29&gt;=$N$27,"Excellent",C29&gt;=$N$28, "Very Good", C29&gt;=$N$29, "Good", C29&gt;=$N$30, "Passed", C29&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <f t="array" ref="H29">_xlfn.IFNA(_xlfn.IFS(C29&gt;=$O$27,"Excellent",C29&gt;=$O$28, "Very Good", C29&gt;=$O$29, "Good", C29&gt;=$O$30, "Passed", C29&lt;$O$30, "Failed"), _xleta.N/A)</f>
         <v>Failed</v>
       </c>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
+      <c r="I29" s="32" t="b">
+        <f t="shared" ref="I29:I38" si="3">AND(C29&gt;50, C30&gt;60)</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="32" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K29" s="32" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L29" s="32"/>
-      <c r="N29" s="33">
+      <c r="M29" s="32"/>
+      <c r="O29" s="33">
         <v>70</v>
       </c>
-      <c r="O29" s="33" t="s">
+      <c r="P29" s="33" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B30" s="29" t="s">
         <v>58</v>
       </c>
@@ -12672,29 +12708,39 @@
         <v>Failed</v>
       </c>
       <c r="F30" s="32" t="str" cm="1">
-        <f t="array" ref="F30">_xlfn.IFS(C30&gt;=$N$27,"Excellent",C30&gt;=$N$28, "Very Good", C30&gt;=$N$29, "Good", C30&gt;=$N$30, "Passed", C30&lt;$N$30, "Failed")</f>
+        <f t="array" ref="F30">_xlfn.IFS(C30&gt;=$O$27,"Excellent",C30&gt;=$O$28, "Very Good", C30&gt;=$O$29, "Good", C30&gt;=$O$30, "Passed", C30&lt;$O$30, "Failed")</f>
         <v>Good</v>
       </c>
       <c r="G30" s="50" t="str" cm="1">
-        <f t="array" ref="G30">IFERROR(_xlfn.IFS(C30&gt;=$N$27,"Excellent",C30&gt;=$N$28, "Very Good", C30&gt;=$N$29, "Good", C30&gt;=$N$30, "Passed", C30&lt;$N$30, "Failed"),"Error")</f>
+        <f t="array" ref="G30">IFERROR(_xlfn.IFS(C30&gt;=$O$27,"Excellent",C30&gt;=$O$28, "Very Good", C30&gt;=$O$29, "Good", C30&gt;=$O$30, "Passed", C30&lt;$O$30, "Failed"),"Error")</f>
         <v>Good</v>
       </c>
       <c r="H30" s="32" t="str" cm="1">
-        <f t="array" ref="H30">_xlfn.IFNA(_xlfn.IFS(C30&gt;=$N$27,"Excellent",C30&gt;=$N$28, "Very Good", C30&gt;=$N$29, "Good", C30&gt;=$N$30, "Passed", C30&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <f t="array" ref="H30">_xlfn.IFNA(_xlfn.IFS(C30&gt;=$O$27,"Excellent",C30&gt;=$O$28, "Very Good", C30&gt;=$O$29, "Good", C30&gt;=$O$30, "Passed", C30&lt;$O$30, "Failed"), _xleta.N/A)</f>
         <v>Good</v>
       </c>
-      <c r="I30" s="32"/>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
+      <c r="I30" s="32" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="J30" s="32" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K30" s="32" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L30" s="32"/>
-      <c r="N30" s="33">
+      <c r="M30" s="32"/>
+      <c r="O30" s="33">
         <v>60</v>
       </c>
-      <c r="O30" s="33" t="s">
+      <c r="P30" s="33" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B31" s="29" t="s">
         <v>59</v>
       </c>
@@ -12707,27 +12753,37 @@
         <v>Failed</v>
       </c>
       <c r="F31" s="32" t="str" cm="1">
-        <f t="array" ref="F31">_xlfn.IFS(C31&gt;=$N$27,"Excellent",C31&gt;=$N$28, "Very Good", C31&gt;=$N$29, "Good", C31&gt;=$N$30, "Passed", C31&lt;$N$30, "Failed")</f>
+        <f t="array" ref="F31">_xlfn.IFS(C31&gt;=$O$27,"Excellent",C31&gt;=$O$28, "Very Good", C31&gt;=$O$29, "Good", C31&gt;=$O$30, "Passed", C31&lt;$O$30, "Failed")</f>
         <v>Passed</v>
       </c>
       <c r="G31" s="50" t="str" cm="1">
-        <f t="array" ref="G31">IFERROR(_xlfn.IFS(C31&gt;=$N$27,"Excellent",C31&gt;=$N$28, "Very Good", C31&gt;=$N$29, "Good", C31&gt;=$N$30, "Passed", C31&lt;$N$30, "Failed"),"Error")</f>
+        <f t="array" ref="G31">IFERROR(_xlfn.IFS(C31&gt;=$O$27,"Excellent",C31&gt;=$O$28, "Very Good", C31&gt;=$O$29, "Good", C31&gt;=$O$30, "Passed", C31&lt;$O$30, "Failed"),"Error")</f>
         <v>Passed</v>
       </c>
       <c r="H31" s="32" t="str" cm="1">
-        <f t="array" ref="H31">_xlfn.IFNA(_xlfn.IFS(C31&gt;=$N$27,"Excellent",C31&gt;=$N$28, "Very Good", C31&gt;=$N$29, "Good", C31&gt;=$N$30, "Passed", C31&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <f t="array" ref="H31">_xlfn.IFNA(_xlfn.IFS(C31&gt;=$O$27,"Excellent",C31&gt;=$O$28, "Very Good", C31&gt;=$O$29, "Good", C31&gt;=$O$30, "Passed", C31&lt;$O$30, "Failed"), _xleta.N/A)</f>
         <v>Passed</v>
       </c>
-      <c r="I31" s="32"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
+      <c r="I31" s="32" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="J31" s="32" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K31" s="32" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L31" s="32"/>
-      <c r="N31" s="33"/>
-      <c r="O31" s="33" t="s">
+      <c r="M31" s="32"/>
+      <c r="O31" s="33"/>
+      <c r="P31" s="33" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B32" s="29" t="s">
         <v>69</v>
       </c>
@@ -12740,25 +12796,35 @@
         <v>Passed</v>
       </c>
       <c r="F32" s="32" t="str" cm="1">
-        <f t="array" ref="F32">_xlfn.IFS(C32&gt;=$N$27,"Excellent",C32&gt;=$N$28, "Very Good", C32&gt;=$N$29, "Good", C32&gt;=$N$30, "Passed", C32&lt;$N$30, "Failed")</f>
+        <f t="array" ref="F32">_xlfn.IFS(C32&gt;=$O$27,"Excellent",C32&gt;=$O$28, "Very Good", C32&gt;=$O$29, "Good", C32&gt;=$O$30, "Passed", C32&lt;$O$30, "Failed")</f>
         <v>Excellent</v>
       </c>
       <c r="G32" s="50" t="str" cm="1">
-        <f t="array" ref="G32">IFERROR(_xlfn.IFS(C32&gt;=$N$27,"Excellent",C32&gt;=$N$28, "Very Good", C32&gt;=$N$29, "Good", C32&gt;=$N$30, "Passed", C32&lt;$N$30, "Failed"),"Error")</f>
+        <f t="array" ref="G32">IFERROR(_xlfn.IFS(C32&gt;=$O$27,"Excellent",C32&gt;=$O$28, "Very Good", C32&gt;=$O$29, "Good", C32&gt;=$O$30, "Passed", C32&lt;$O$30, "Failed"),"Error")</f>
         <v>Excellent</v>
       </c>
       <c r="H32" s="32" t="str" cm="1">
-        <f t="array" ref="H32">_xlfn.IFNA(_xlfn.IFS(C32&gt;=$N$27,"Excellent",C32&gt;=$N$28, "Very Good", C32&gt;=$N$29, "Good", C32&gt;=$N$30, "Passed", C32&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <f t="array" ref="H32">_xlfn.IFNA(_xlfn.IFS(C32&gt;=$O$27,"Excellent",C32&gt;=$O$28, "Very Good", C32&gt;=$O$29, "Good", C32&gt;=$O$30, "Passed", C32&lt;$O$30, "Failed"), _xleta.N/A)</f>
         <v>Excellent</v>
       </c>
-      <c r="I32" s="32"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="32"/>
+      <c r="I32" s="32" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="32" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K32" s="32" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L32" s="32"/>
-      <c r="N32" s="34"/>
+      <c r="M32" s="32"/>
       <c r="O32" s="34"/>
-    </row>
-    <row r="33" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="P32" s="34"/>
+    </row>
+    <row r="33" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B33" s="29" t="s">
         <v>94</v>
       </c>
@@ -12771,29 +12837,39 @@
         <v>Failed</v>
       </c>
       <c r="F33" s="32" t="str" cm="1">
-        <f t="array" ref="F33">_xlfn.IFS(C33&gt;=$N$27,"Excellent",C33&gt;=$N$28, "Very Good", C33&gt;=$N$29, "Good", C33&gt;=$N$30, "Passed", C33&lt;$N$30, "Failed")</f>
+        <f t="array" ref="F33">_xlfn.IFS(C33&gt;=$O$27,"Excellent",C33&gt;=$O$28, "Very Good", C33&gt;=$O$29, "Good", C33&gt;=$O$30, "Passed", C33&lt;$O$30, "Failed")</f>
         <v>Failed</v>
       </c>
       <c r="G33" s="50" t="str" cm="1">
-        <f t="array" ref="G33">IFERROR(_xlfn.IFS(C33&gt;=$N$27,"Excellent",C33&gt;=$N$28, "Very Good", C33&gt;=$N$29, "Good", C33&gt;=$N$30, "Passed", C33&lt;$N$30, "Failed"),"Error")</f>
+        <f t="array" ref="G33">IFERROR(_xlfn.IFS(C33&gt;=$O$27,"Excellent",C33&gt;=$O$28, "Very Good", C33&gt;=$O$29, "Good", C33&gt;=$O$30, "Passed", C33&lt;$O$30, "Failed"),"Error")</f>
         <v>Failed</v>
       </c>
       <c r="H33" s="32" t="str" cm="1">
-        <f t="array" ref="H33">_xlfn.IFNA(_xlfn.IFS(C33&gt;=$N$27,"Excellent",C33&gt;=$N$28, "Very Good", C33&gt;=$N$29, "Good", C33&gt;=$N$30, "Passed", C33&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <f t="array" ref="H33">_xlfn.IFNA(_xlfn.IFS(C33&gt;=$O$27,"Excellent",C33&gt;=$O$28, "Very Good", C33&gt;=$O$29, "Good", C33&gt;=$O$30, "Passed", C33&lt;$O$30, "Failed"), _xleta.N/A)</f>
         <v>Failed</v>
       </c>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
+      <c r="I33" s="32" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="32" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K33" s="32" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L33" s="32"/>
-      <c r="N33" s="35" t="s">
+      <c r="M33" s="32"/>
+      <c r="O33" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="O33" s="36">
+      <c r="P33" s="36">
         <v>0.12</v>
       </c>
     </row>
-    <row r="34" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B34" s="29" t="s">
         <v>96</v>
       </c>
@@ -12806,29 +12882,39 @@
         <v>Passed</v>
       </c>
       <c r="F34" s="32" t="str" cm="1">
-        <f t="array" ref="F34">_xlfn.IFS(C34&gt;=$N$27,"Excellent",C34&gt;=$N$28, "Very Good", C34&gt;=$N$29, "Good", C34&gt;=$N$30, "Passed", C34&lt;$N$30, "Failed")</f>
+        <f t="array" ref="F34">_xlfn.IFS(C34&gt;=$O$27,"Excellent",C34&gt;=$O$28, "Very Good", C34&gt;=$O$29, "Good", C34&gt;=$O$30, "Passed", C34&lt;$O$30, "Failed")</f>
         <v>Very Good</v>
       </c>
       <c r="G34" s="50" t="str" cm="1">
-        <f t="array" ref="G34">IFERROR(_xlfn.IFS(C34&gt;=$N$27,"Excellent",C34&gt;=$N$28, "Very Good", C34&gt;=$N$29, "Good", C34&gt;=$N$30, "Passed", C34&lt;$N$30, "Failed"),"Error")</f>
+        <f t="array" ref="G34">IFERROR(_xlfn.IFS(C34&gt;=$O$27,"Excellent",C34&gt;=$O$28, "Very Good", C34&gt;=$O$29, "Good", C34&gt;=$O$30, "Passed", C34&lt;$O$30, "Failed"),"Error")</f>
         <v>Very Good</v>
       </c>
       <c r="H34" s="32" t="str" cm="1">
-        <f t="array" ref="H34">_xlfn.IFNA(_xlfn.IFS(C34&gt;=$N$27,"Excellent",C34&gt;=$N$28, "Very Good", C34&gt;=$N$29, "Good", C34&gt;=$N$30, "Passed", C34&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <f t="array" ref="H34">_xlfn.IFNA(_xlfn.IFS(C34&gt;=$O$27,"Excellent",C34&gt;=$O$28, "Very Good", C34&gt;=$O$29, "Good", C34&gt;=$O$30, "Passed", C34&lt;$O$30, "Failed"), _xleta.N/A)</f>
         <v>Very Good</v>
       </c>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
+      <c r="I34" s="32" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="32" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K34" s="32" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L34" s="32"/>
-      <c r="N34" s="37" t="s">
+      <c r="M34" s="32"/>
+      <c r="O34" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="O34" s="36">
+      <c r="P34" s="36">
         <v>0.08</v>
       </c>
     </row>
-    <row r="35" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B35" s="29" t="s">
         <v>98</v>
       </c>
@@ -12841,29 +12927,39 @@
         <v>Failed</v>
       </c>
       <c r="F35" s="32" t="str" cm="1">
-        <f t="array" ref="F35">_xlfn.IFS(C35&gt;=$N$27,"Excellent",C35&gt;=$N$28, "Very Good", C35&gt;=$N$29, "Good", C35&gt;=$N$30, "Passed", C35&lt;$N$30, "Failed")</f>
+        <f t="array" ref="F35">_xlfn.IFS(C35&gt;=$O$27,"Excellent",C35&gt;=$O$28, "Very Good", C35&gt;=$O$29, "Good", C35&gt;=$O$30, "Passed", C35&lt;$O$30, "Failed")</f>
         <v>Failed</v>
       </c>
       <c r="G35" s="50" t="str" cm="1">
-        <f t="array" ref="G35">IFERROR(_xlfn.IFS(C35&gt;=$N$27,"Excellent",C35&gt;=$N$28, "Very Good", C35&gt;=$N$29, "Good", C35&gt;=$N$30, "Passed", C35&lt;$N$30, "Failed"),"Error")</f>
+        <f t="array" ref="G35">IFERROR(_xlfn.IFS(C35&gt;=$O$27,"Excellent",C35&gt;=$O$28, "Very Good", C35&gt;=$O$29, "Good", C35&gt;=$O$30, "Passed", C35&lt;$O$30, "Failed"),"Error")</f>
         <v>Failed</v>
       </c>
       <c r="H35" s="32" t="str" cm="1">
-        <f t="array" ref="H35">_xlfn.IFNA(_xlfn.IFS(C35&gt;=$N$27,"Excellent",C35&gt;=$N$28, "Very Good", C35&gt;=$N$29, "Good", C35&gt;=$N$30, "Passed", C35&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <f t="array" ref="H35">_xlfn.IFNA(_xlfn.IFS(C35&gt;=$O$27,"Excellent",C35&gt;=$O$28, "Very Good", C35&gt;=$O$29, "Good", C35&gt;=$O$30, "Passed", C35&lt;$O$30, "Failed"), _xleta.N/A)</f>
         <v>Failed</v>
       </c>
-      <c r="I35" s="32"/>
-      <c r="J35" s="32"/>
-      <c r="K35" s="32"/>
+      <c r="I35" s="32" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="32" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K35" s="32" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L35" s="32"/>
-      <c r="N35" s="37" t="s">
+      <c r="M35" s="32"/>
+      <c r="O35" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="O35" s="36">
+      <c r="P35" s="36">
         <v>0.05</v>
       </c>
     </row>
-    <row r="36" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B36" s="29" t="s">
         <v>100</v>
       </c>
@@ -12876,29 +12972,39 @@
         <v>Failed</v>
       </c>
       <c r="F36" s="32" t="str" cm="1">
-        <f t="array" ref="F36">_xlfn.IFS(C36&gt;=$N$27,"Excellent",C36&gt;=$N$28, "Very Good", C36&gt;=$N$29, "Good", C36&gt;=$N$30, "Passed", C36&lt;$N$30, "Failed")</f>
+        <f t="array" ref="F36">_xlfn.IFS(C36&gt;=$O$27,"Excellent",C36&gt;=$O$28, "Very Good", C36&gt;=$O$29, "Good", C36&gt;=$O$30, "Passed", C36&lt;$O$30, "Failed")</f>
         <v>Passed</v>
       </c>
       <c r="G36" s="50" t="str" cm="1">
-        <f t="array" ref="G36">IFERROR(_xlfn.IFS(C36&gt;=$N$27,"Excellent",C36&gt;=$N$28, "Very Good", C36&gt;=$N$29, "Good", C36&gt;=$N$30, "Passed", C36&lt;$N$30, "Failed"),"Error")</f>
+        <f t="array" ref="G36">IFERROR(_xlfn.IFS(C36&gt;=$O$27,"Excellent",C36&gt;=$O$28, "Very Good", C36&gt;=$O$29, "Good", C36&gt;=$O$30, "Passed", C36&lt;$O$30, "Failed"),"Error")</f>
         <v>Passed</v>
       </c>
       <c r="H36" s="32" t="str" cm="1">
-        <f t="array" ref="H36">_xlfn.IFNA(_xlfn.IFS(C36&gt;=$N$27,"Excellent",C36&gt;=$N$28, "Very Good", C36&gt;=$N$29, "Good", C36&gt;=$N$30, "Passed", C36&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <f t="array" ref="H36">_xlfn.IFNA(_xlfn.IFS(C36&gt;=$O$27,"Excellent",C36&gt;=$O$28, "Very Good", C36&gt;=$O$29, "Good", C36&gt;=$O$30, "Passed", C36&lt;$O$30, "Failed"), _xleta.N/A)</f>
         <v>Passed</v>
       </c>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
+      <c r="I36" s="32" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="32" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="32" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
       <c r="L36" s="32"/>
-      <c r="N36" s="37" t="s">
+      <c r="M36" s="32"/>
+      <c r="O36" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="O36" s="36">
+      <c r="P36" s="36">
         <v>0.03</v>
       </c>
     </row>
-    <row r="37" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B37" s="29" t="s">
         <v>102</v>
       </c>
@@ -12911,23 +13017,33 @@
         <v>Failed</v>
       </c>
       <c r="F37" s="32" t="str" cm="1">
-        <f t="array" ref="F37">_xlfn.IFS(C37&gt;=$N$27,"Excellent",C37&gt;=$N$28, "Very Good", C37&gt;=$N$29, "Good", C37&gt;=$N$30, "Passed", C37&lt;$N$30, "Failed")</f>
+        <f t="array" ref="F37">_xlfn.IFS(C37&gt;=$O$27,"Excellent",C37&gt;=$O$28, "Very Good", C37&gt;=$O$29, "Good", C37&gt;=$O$30, "Passed", C37&lt;$O$30, "Failed")</f>
         <v>Failed</v>
       </c>
       <c r="G37" s="50" t="str" cm="1">
-        <f t="array" ref="G37">IFERROR(_xlfn.IFS(C37&gt;=$N$27,"Excellent",C37&gt;=$N$28, "Very Good", C37&gt;=$N$29, "Good", C37&gt;=$N$30, "Passed", C37&lt;$N$30, "Failed"),"Error")</f>
+        <f t="array" ref="G37">IFERROR(_xlfn.IFS(C37&gt;=$O$27,"Excellent",C37&gt;=$O$28, "Very Good", C37&gt;=$O$29, "Good", C37&gt;=$O$30, "Passed", C37&lt;$O$30, "Failed"),"Error")</f>
         <v>Failed</v>
       </c>
       <c r="H37" s="32" t="str" cm="1">
-        <f t="array" ref="H37">_xlfn.IFNA(_xlfn.IFS(C37&gt;=$N$27,"Excellent",C37&gt;=$N$28, "Very Good", C37&gt;=$N$29, "Good", C37&gt;=$N$30, "Passed", C37&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <f t="array" ref="H37">_xlfn.IFNA(_xlfn.IFS(C37&gt;=$O$27,"Excellent",C37&gt;=$O$28, "Very Good", C37&gt;=$O$29, "Good", C37&gt;=$O$30, "Passed", C37&lt;$O$30, "Failed"), _xleta.N/A)</f>
         <v>Failed</v>
       </c>
-      <c r="I37" s="32"/>
-      <c r="J37" s="32"/>
-      <c r="K37" s="32"/>
+      <c r="I37" s="32" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="32" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K37" s="32" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L37" s="32"/>
-    </row>
-    <row r="38" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="M37" s="32"/>
+    </row>
+    <row r="38" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B38" s="29" t="s">
         <v>103</v>
       </c>
@@ -12940,28 +13056,38 @@
         <v>Failed</v>
       </c>
       <c r="F38" s="32" t="str" cm="1">
-        <f t="array" ref="F38">_xlfn.IFS(C38&gt;=$N$27,"Excellent",C38&gt;=$N$28, "Very Good", C38&gt;=$N$29, "Good", C38&gt;=$N$30, "Passed", C38&lt;$N$30, "Failed")</f>
+        <f t="array" ref="F38">_xlfn.IFS(C38&gt;=$O$27,"Excellent",C38&gt;=$O$28, "Very Good", C38&gt;=$O$29, "Good", C38&gt;=$O$30, "Passed", C38&lt;$O$30, "Failed")</f>
         <v>Good</v>
       </c>
       <c r="G38" s="50" t="str" cm="1">
-        <f t="array" ref="G38">IFERROR(_xlfn.IFS(C38&gt;=$N$27,"Excellent",C38&gt;=$N$28, "Very Good", C38&gt;=$N$29, "Good", C38&gt;=$N$30, "Passed", C38&lt;$N$30, "Failed"),"Error")</f>
+        <f t="array" ref="G38">IFERROR(_xlfn.IFS(C38&gt;=$O$27,"Excellent",C38&gt;=$O$28, "Very Good", C38&gt;=$O$29, "Good", C38&gt;=$O$30, "Passed", C38&lt;$O$30, "Failed"),"Error")</f>
         <v>Good</v>
       </c>
       <c r="H38" s="32" t="str" cm="1">
-        <f t="array" ref="H38">_xlfn.IFNA(_xlfn.IFS(C38&gt;=$N$27,"Excellent",C38&gt;=$N$28, "Very Good", C38&gt;=$N$29, "Good", C38&gt;=$N$30, "Passed", C38&lt;$N$30, "Failed"), _xleta.N/A)</f>
+        <f t="array" ref="H38">_xlfn.IFNA(_xlfn.IFS(C38&gt;=$O$27,"Excellent",C38&gt;=$O$28, "Very Good", C38&gt;=$O$29, "Good", C38&gt;=$O$30, "Passed", C38&lt;$O$30, "Failed"), _xleta.N/A)</f>
         <v>Good</v>
       </c>
-      <c r="I38" s="32"/>
-      <c r="J38" s="32"/>
-      <c r="K38" s="32"/>
+      <c r="I38" s="32" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="32" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K38" s="32" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L38" s="32"/>
-    </row>
-    <row r="46" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="M38" s="32"/>
+    </row>
+    <row r="46" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B46" s="38" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="48" spans="2:15" ht="18" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:16" ht="18" x14ac:dyDescent="0.3">
       <c r="C48" s="51" t="s">
         <v>135</v>
       </c>
@@ -13016,7 +13142,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="53" spans="3:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C53" s="54" t="e">
         <v>#N/A</v>
       </c>
@@ -13038,7 +13164,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="55" spans="3:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C55" s="54" t="e">
         <v>#NULL!</v>
       </c>
@@ -13051,7 +13177,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="O26:P26"/>
     <mergeCell ref="A1:R1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA37B55-97C0-4073-BDE2-AADE5A25E368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{929EFC89-7962-4A14-BD4F-789540A286C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="D9" s="40">
         <f ca="1">NOW()</f>
-        <v>46294.112390509261</v>
+        <v>46294.113413541665</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="18" x14ac:dyDescent="0.35">
@@ -12596,7 +12596,10 @@
         <f>NOT(J27)</f>
         <v>0</v>
       </c>
-      <c r="L27" s="32"/>
+      <c r="L27" s="32" t="str">
+        <f>IF(AND(C27&gt;50,C28&gt;40),"Good","Bad")</f>
+        <v>Good</v>
+      </c>
       <c r="M27" s="32"/>
       <c r="O27" s="33">
         <v>90</v>
@@ -12641,7 +12644,10 @@
         <f t="shared" ref="K28:K38" si="2">NOT(J28)</f>
         <v>0</v>
       </c>
-      <c r="L28" s="32"/>
+      <c r="L28" s="32" t="str">
+        <f t="shared" ref="L28:L38" si="3">IF(AND(C28&gt;50,C29&gt;40),"Good","Bad")</f>
+        <v>Bad</v>
+      </c>
       <c r="M28" s="32"/>
       <c r="O28" s="33">
         <v>80</v>
@@ -12675,7 +12681,7 @@
         <v>Failed</v>
       </c>
       <c r="I29" s="32" t="b">
-        <f t="shared" ref="I29:I38" si="3">AND(C29&gt;50, C30&gt;60)</f>
+        <f t="shared" ref="I29:I38" si="4">AND(C29&gt;50, C30&gt;60)</f>
         <v>0</v>
       </c>
       <c r="J29" s="32" t="b">
@@ -12686,7 +12692,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="32"/>
+      <c r="L29" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>Bad</v>
+      </c>
       <c r="M29" s="32"/>
       <c r="O29" s="33">
         <v>70</v>
@@ -12720,7 +12729,7 @@
         <v>Good</v>
       </c>
       <c r="I30" s="32" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J30" s="32" t="b">
@@ -12731,7 +12740,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L30" s="32"/>
+      <c r="L30" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>Good</v>
+      </c>
       <c r="M30" s="32"/>
       <c r="O30" s="33">
         <v>60</v>
@@ -12765,7 +12777,7 @@
         <v>Passed</v>
       </c>
       <c r="I31" s="32" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J31" s="32" t="b">
@@ -12776,7 +12788,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L31" s="32"/>
+      <c r="L31" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>Good</v>
+      </c>
       <c r="M31" s="32"/>
       <c r="O31" s="33"/>
       <c r="P31" s="33" t="s">
@@ -12808,7 +12823,7 @@
         <v>Excellent</v>
       </c>
       <c r="I32" s="32" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J32" s="32" t="b">
@@ -12819,7 +12834,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L32" s="32"/>
+      <c r="L32" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>Good</v>
+      </c>
       <c r="M32" s="32"/>
       <c r="O32" s="34"/>
       <c r="P32" s="34"/>
@@ -12849,7 +12867,7 @@
         <v>Failed</v>
       </c>
       <c r="I33" s="32" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J33" s="32" t="b">
@@ -12860,7 +12878,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="32"/>
+      <c r="L33" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>Bad</v>
+      </c>
       <c r="M33" s="32"/>
       <c r="O33" s="35" t="s">
         <v>95</v>
@@ -12894,7 +12915,7 @@
         <v>Very Good</v>
       </c>
       <c r="I34" s="32" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J34" s="32" t="b">
@@ -12905,7 +12926,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L34" s="32"/>
+      <c r="L34" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>Bad</v>
+      </c>
       <c r="M34" s="32"/>
       <c r="O34" s="37" t="s">
         <v>97</v>
@@ -12939,7 +12963,7 @@
         <v>Failed</v>
       </c>
       <c r="I35" s="32" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J35" s="32" t="b">
@@ -12950,7 +12974,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L35" s="32"/>
+      <c r="L35" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>Bad</v>
+      </c>
       <c r="M35" s="32"/>
       <c r="O35" s="37" t="s">
         <v>99</v>
@@ -12984,7 +13011,7 @@
         <v>Passed</v>
       </c>
       <c r="I36" s="32" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J36" s="32" t="b">
@@ -12995,7 +13022,10 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="L36" s="32"/>
+      <c r="L36" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>Bad</v>
+      </c>
       <c r="M36" s="32"/>
       <c r="O36" s="37" t="s">
         <v>101</v>
@@ -13029,7 +13059,7 @@
         <v>Failed</v>
       </c>
       <c r="I37" s="32" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J37" s="32" t="b">
@@ -13040,7 +13070,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L37" s="32"/>
+      <c r="L37" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>Bad</v>
+      </c>
       <c r="M37" s="32"/>
     </row>
     <row r="38" spans="2:16" ht="18" x14ac:dyDescent="0.35">
@@ -13068,7 +13101,7 @@
         <v>Good</v>
       </c>
       <c r="I38" s="32" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J38" s="32" t="b">
@@ -13079,7 +13112,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L38" s="32"/>
+      <c r="L38" s="32" t="str">
+        <f t="shared" si="3"/>
+        <v>Bad</v>
+      </c>
       <c r="M38" s="32"/>
     </row>
     <row r="46" spans="2:16" ht="18" x14ac:dyDescent="0.35">

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{929EFC89-7962-4A14-BD4F-789540A286C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5BF0D1-EA4F-4383-9EE8-EAAB94185C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="D9" s="40">
         <f ca="1">NOW()</f>
-        <v>46294.113413541665</v>
+        <v>46294.115409259262</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="18" x14ac:dyDescent="0.35">
@@ -12600,7 +12600,10 @@
         <f>IF(AND(C27&gt;50,C28&gt;40),"Good","Bad")</f>
         <v>Good</v>
       </c>
-      <c r="M27" s="32"/>
+      <c r="M27" s="32" t="str" cm="1">
+        <f t="array" ref="M27">_xlfn.SWITCH(C27,60,"Good",81,"Excellent",50,"Passed")</f>
+        <v>Good</v>
+      </c>
       <c r="O27" s="33">
         <v>90</v>
       </c>
@@ -12648,7 +12651,10 @@
         <f t="shared" ref="L28:L38" si="3">IF(AND(C28&gt;50,C29&gt;40),"Good","Bad")</f>
         <v>Bad</v>
       </c>
-      <c r="M28" s="32"/>
+      <c r="M28" s="32" t="str" cm="1">
+        <f t="array" ref="M28">_xlfn.SWITCH(C28,60,"Good",81,"Excellent",50,"Passed")</f>
+        <v>Excellent</v>
+      </c>
       <c r="O28" s="33">
         <v>80</v>
       </c>
@@ -12696,7 +12702,10 @@
         <f t="shared" si="3"/>
         <v>Bad</v>
       </c>
-      <c r="M29" s="32"/>
+      <c r="M29" s="32" t="e" cm="1">
+        <f t="array" ref="M29">_xlfn.SWITCH(C29,60,"Good",81,"Excellent",50,"Passed")</f>
+        <v>#N/A</v>
+      </c>
       <c r="O29" s="33">
         <v>70</v>
       </c>
@@ -12744,7 +12753,10 @@
         <f t="shared" si="3"/>
         <v>Good</v>
       </c>
-      <c r="M30" s="32"/>
+      <c r="M30" s="32" t="e" cm="1">
+        <f t="array" ref="M30">_xlfn.SWITCH(C30,60,"Good",81,"Excellent",50,"Passed")</f>
+        <v>#N/A</v>
+      </c>
       <c r="O30" s="33">
         <v>60</v>
       </c>
@@ -12792,7 +12804,10 @@
         <f t="shared" si="3"/>
         <v>Good</v>
       </c>
-      <c r="M31" s="32"/>
+      <c r="M31" s="32" t="e" cm="1">
+        <f t="array" ref="M31">_xlfn.SWITCH(C31,60,"Good",81,"Excellent",50,"Passed")</f>
+        <v>#N/A</v>
+      </c>
       <c r="O31" s="33"/>
       <c r="P31" s="33" t="s">
         <v>93</v>
@@ -12838,7 +12853,10 @@
         <f t="shared" si="3"/>
         <v>Good</v>
       </c>
-      <c r="M32" s="32"/>
+      <c r="M32" s="32" t="e" cm="1">
+        <f t="array" ref="M32">_xlfn.SWITCH(C32,60,"Good",81,"Excellent",50,"Passed")</f>
+        <v>#N/A</v>
+      </c>
       <c r="O32" s="34"/>
       <c r="P32" s="34"/>
     </row>
@@ -12882,7 +12900,10 @@
         <f t="shared" si="3"/>
         <v>Bad</v>
       </c>
-      <c r="M33" s="32"/>
+      <c r="M33" s="32" t="str" cm="1">
+        <f t="array" ref="M33">_xlfn.SWITCH(C33,60,"Good",81,"Excellent",50,"Passed")</f>
+        <v>Passed</v>
+      </c>
       <c r="O33" s="35" t="s">
         <v>95</v>
       </c>
@@ -12930,7 +12951,10 @@
         <f t="shared" si="3"/>
         <v>Bad</v>
       </c>
-      <c r="M34" s="32"/>
+      <c r="M34" s="32" t="e" cm="1">
+        <f t="array" ref="M34">_xlfn.SWITCH(C34,60,"Good",81,"Excellent",50,"Passed")</f>
+        <v>#N/A</v>
+      </c>
       <c r="O34" s="37" t="s">
         <v>97</v>
       </c>
@@ -12978,7 +13002,10 @@
         <f t="shared" si="3"/>
         <v>Bad</v>
       </c>
-      <c r="M35" s="32"/>
+      <c r="M35" s="32" t="e" cm="1">
+        <f t="array" ref="M35">_xlfn.SWITCH(C35,60,"Good",81,"Excellent",50,"Passed")</f>
+        <v>#N/A</v>
+      </c>
       <c r="O35" s="37" t="s">
         <v>99</v>
       </c>
@@ -13026,7 +13053,10 @@
         <f t="shared" si="3"/>
         <v>Bad</v>
       </c>
-      <c r="M36" s="32"/>
+      <c r="M36" s="32" t="e" cm="1">
+        <f t="array" ref="M36">_xlfn.SWITCH(C36,60,"Good",81,"Excellent",50,"Passed")</f>
+        <v>#N/A</v>
+      </c>
       <c r="O36" s="37" t="s">
         <v>101</v>
       </c>
@@ -13074,7 +13104,10 @@
         <f t="shared" si="3"/>
         <v>Bad</v>
       </c>
-      <c r="M37" s="32"/>
+      <c r="M37" s="32" t="e" cm="1">
+        <f t="array" ref="M37">_xlfn.SWITCH(C37,60,"Good",81,"Excellent",50,"Passed")</f>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="38" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B38" s="29" t="s">
@@ -13116,7 +13149,10 @@
         <f t="shared" si="3"/>
         <v>Bad</v>
       </c>
-      <c r="M38" s="32"/>
+      <c r="M38" s="32" t="e" cm="1">
+        <f t="array" ref="M38">_xlfn.SWITCH(C38,60,"Good",81,"Excellent",50,"Passed")</f>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="46" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B46" s="38" t="s">

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5BF0D1-EA4F-4383-9EE8-EAAB94185C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7136921-84BA-4CEF-86A6-94411C8E4A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="D9" s="40">
         <f ca="1">NOW()</f>
-        <v>46294.115409259262</v>
+        <v>46294.116408449074</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="18" x14ac:dyDescent="0.35">
@@ -12601,7 +12601,7 @@
         <v>Good</v>
       </c>
       <c r="M27" s="32" t="str" cm="1">
-        <f t="array" ref="M27">_xlfn.SWITCH(C27,60,"Good",81,"Excellent",50,"Passed")</f>
+        <f t="array" ref="M27">IFERROR(_xlfn.SWITCH(C27,60,"Good",81,"Excellent",50,"Passed"),"Failed")</f>
         <v>Good</v>
       </c>
       <c r="O27" s="33">
@@ -12652,7 +12652,7 @@
         <v>Bad</v>
       </c>
       <c r="M28" s="32" t="str" cm="1">
-        <f t="array" ref="M28">_xlfn.SWITCH(C28,60,"Good",81,"Excellent",50,"Passed")</f>
+        <f t="array" ref="M28">IFERROR(_xlfn.SWITCH(C28,60,"Good",81,"Excellent",50,"Passed"),"Failed")</f>
         <v>Excellent</v>
       </c>
       <c r="O28" s="33">
@@ -12702,9 +12702,9 @@
         <f t="shared" si="3"/>
         <v>Bad</v>
       </c>
-      <c r="M29" s="32" t="e" cm="1">
-        <f t="array" ref="M29">_xlfn.SWITCH(C29,60,"Good",81,"Excellent",50,"Passed")</f>
-        <v>#N/A</v>
+      <c r="M29" s="32" t="str" cm="1">
+        <f t="array" ref="M29">IFERROR(_xlfn.SWITCH(C29,60,"Good",81,"Excellent",50,"Passed"),"Failed")</f>
+        <v>Failed</v>
       </c>
       <c r="O29" s="33">
         <v>70</v>
@@ -12753,9 +12753,9 @@
         <f t="shared" si="3"/>
         <v>Good</v>
       </c>
-      <c r="M30" s="32" t="e" cm="1">
-        <f t="array" ref="M30">_xlfn.SWITCH(C30,60,"Good",81,"Excellent",50,"Passed")</f>
-        <v>#N/A</v>
+      <c r="M30" s="32" t="str" cm="1">
+        <f t="array" ref="M30">IFERROR(_xlfn.SWITCH(C30,60,"Good",81,"Excellent",50,"Passed"),"Failed")</f>
+        <v>Failed</v>
       </c>
       <c r="O30" s="33">
         <v>60</v>
@@ -12804,9 +12804,9 @@
         <f t="shared" si="3"/>
         <v>Good</v>
       </c>
-      <c r="M31" s="32" t="e" cm="1">
-        <f t="array" ref="M31">_xlfn.SWITCH(C31,60,"Good",81,"Excellent",50,"Passed")</f>
-        <v>#N/A</v>
+      <c r="M31" s="32" t="str" cm="1">
+        <f t="array" ref="M31">IFERROR(_xlfn.SWITCH(C31,60,"Good",81,"Excellent",50,"Passed"),"Failed")</f>
+        <v>Failed</v>
       </c>
       <c r="O31" s="33"/>
       <c r="P31" s="33" t="s">
@@ -12853,9 +12853,9 @@
         <f t="shared" si="3"/>
         <v>Good</v>
       </c>
-      <c r="M32" s="32" t="e" cm="1">
-        <f t="array" ref="M32">_xlfn.SWITCH(C32,60,"Good",81,"Excellent",50,"Passed")</f>
-        <v>#N/A</v>
+      <c r="M32" s="32" t="str" cm="1">
+        <f t="array" ref="M32">IFERROR(_xlfn.SWITCH(C32,60,"Good",81,"Excellent",50,"Passed"),"Failed")</f>
+        <v>Failed</v>
       </c>
       <c r="O32" s="34"/>
       <c r="P32" s="34"/>
@@ -12901,7 +12901,7 @@
         <v>Bad</v>
       </c>
       <c r="M33" s="32" t="str" cm="1">
-        <f t="array" ref="M33">_xlfn.SWITCH(C33,60,"Good",81,"Excellent",50,"Passed")</f>
+        <f t="array" ref="M33">IFERROR(_xlfn.SWITCH(C33,60,"Good",81,"Excellent",50,"Passed"),"Failed")</f>
         <v>Passed</v>
       </c>
       <c r="O33" s="35" t="s">
@@ -12951,9 +12951,9 @@
         <f t="shared" si="3"/>
         <v>Bad</v>
       </c>
-      <c r="M34" s="32" t="e" cm="1">
-        <f t="array" ref="M34">_xlfn.SWITCH(C34,60,"Good",81,"Excellent",50,"Passed")</f>
-        <v>#N/A</v>
+      <c r="M34" s="32" t="str" cm="1">
+        <f t="array" ref="M34">IFERROR(_xlfn.SWITCH(C34,60,"Good",81,"Excellent",50,"Passed"),"Failed")</f>
+        <v>Failed</v>
       </c>
       <c r="O34" s="37" t="s">
         <v>97</v>
@@ -13002,9 +13002,9 @@
         <f t="shared" si="3"/>
         <v>Bad</v>
       </c>
-      <c r="M35" s="32" t="e" cm="1">
-        <f t="array" ref="M35">_xlfn.SWITCH(C35,60,"Good",81,"Excellent",50,"Passed")</f>
-        <v>#N/A</v>
+      <c r="M35" s="32" t="str" cm="1">
+        <f t="array" ref="M35">IFERROR(_xlfn.SWITCH(C35,60,"Good",81,"Excellent",50,"Passed"),"Failed")</f>
+        <v>Failed</v>
       </c>
       <c r="O35" s="37" t="s">
         <v>99</v>
@@ -13053,9 +13053,9 @@
         <f t="shared" si="3"/>
         <v>Bad</v>
       </c>
-      <c r="M36" s="32" t="e" cm="1">
-        <f t="array" ref="M36">_xlfn.SWITCH(C36,60,"Good",81,"Excellent",50,"Passed")</f>
-        <v>#N/A</v>
+      <c r="M36" s="32" t="str" cm="1">
+        <f t="array" ref="M36">IFERROR(_xlfn.SWITCH(C36,60,"Good",81,"Excellent",50,"Passed"),"Failed")</f>
+        <v>Failed</v>
       </c>
       <c r="O36" s="37" t="s">
         <v>101</v>
@@ -13104,9 +13104,9 @@
         <f t="shared" si="3"/>
         <v>Bad</v>
       </c>
-      <c r="M37" s="32" t="e" cm="1">
-        <f t="array" ref="M37">_xlfn.SWITCH(C37,60,"Good",81,"Excellent",50,"Passed")</f>
-        <v>#N/A</v>
+      <c r="M37" s="32" t="str" cm="1">
+        <f t="array" ref="M37">IFERROR(_xlfn.SWITCH(C37,60,"Good",81,"Excellent",50,"Passed"),"Failed")</f>
+        <v>Failed</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="18" x14ac:dyDescent="0.35">
@@ -13149,9 +13149,9 @@
         <f t="shared" si="3"/>
         <v>Bad</v>
       </c>
-      <c r="M38" s="32" t="e" cm="1">
-        <f t="array" ref="M38">_xlfn.SWITCH(C38,60,"Good",81,"Excellent",50,"Passed")</f>
-        <v>#N/A</v>
+      <c r="M38" s="32" t="str" cm="1">
+        <f t="array" ref="M38">IFERROR(_xlfn.SWITCH(C38,60,"Good",81,"Excellent",50,"Passed"),"Failed")</f>
+        <v>Failed</v>
       </c>
     </row>
     <row r="46" spans="2:16" ht="18" x14ac:dyDescent="0.35">

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7136921-84BA-4CEF-86A6-94411C8E4A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0413F0-9079-40F3-8245-0C91DCCDBEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="D9" s="40">
         <f ca="1">NOW()</f>
-        <v>46294.116408449074</v>
+        <v>46294.117272569441</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="18" x14ac:dyDescent="0.35">

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0413F0-9079-40F3-8245-0C91DCCDBEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2F6CCE-3AC4-47D7-86F8-961C9720A066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Date and Time " sheetId="19" r:id="rId1"/>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="D9" s="40">
         <f ca="1">NOW()</f>
-        <v>46294.117272569441</v>
+        <v>46294.123200810187</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="18" x14ac:dyDescent="0.35">
@@ -13837,10 +13837,7 @@
       <c r="K27" s="12">
         <v>15</v>
       </c>
-      <c r="L27" s="57" t="str">
-        <f>VLOOKUP(K27,$B$21:$I$46,2,FALSE)</f>
-        <v>Sayed Gohar</v>
-      </c>
+      <c r="L27" s="57"/>
       <c r="M27" s="6"/>
       <c r="N27" s="11" t="s">
         <v>10</v>
@@ -13876,10 +13873,7 @@
       <c r="K28" s="11">
         <v>10</v>
       </c>
-      <c r="L28" s="57" t="str">
-        <f t="shared" ref="L28:L41" si="1">VLOOKUP(K28,$B$21:$I$46,2,FALSE)</f>
-        <v>Yousef Amr</v>
-      </c>
+      <c r="L28" s="57"/>
       <c r="M28" s="6"/>
       <c r="N28" s="11" t="s">
         <v>11</v>
@@ -13915,10 +13909,7 @@
       <c r="K29" s="11">
         <v>7</v>
       </c>
-      <c r="L29" s="57" t="str">
-        <f t="shared" si="1"/>
-        <v>Bakr Elmallwany</v>
-      </c>
+      <c r="L29" s="57"/>
       <c r="M29" s="6"/>
       <c r="N29" s="11" t="s">
         <v>12</v>
@@ -13954,10 +13945,7 @@
       <c r="K30" s="11">
         <v>11</v>
       </c>
-      <c r="L30" s="57" t="str">
-        <f t="shared" si="1"/>
-        <v>Omar Mohamed</v>
-      </c>
+      <c r="L30" s="57"/>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
     </row>
@@ -13991,10 +13979,7 @@
       <c r="K31" s="11">
         <v>5</v>
       </c>
-      <c r="L31" s="57" t="str">
-        <f t="shared" si="1"/>
-        <v>Hesham Mostafa</v>
-      </c>
+      <c r="L31" s="57"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
@@ -14028,10 +14013,7 @@
       <c r="K32" s="11">
         <v>6</v>
       </c>
-      <c r="L32" s="57" t="str">
-        <f t="shared" si="1"/>
-        <v>Ibrahim Ali</v>
-      </c>
+      <c r="L32" s="57"/>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
     </row>
@@ -14065,10 +14047,7 @@
       <c r="K33" s="11">
         <v>12</v>
       </c>
-      <c r="L33" s="57" t="str">
-        <f t="shared" si="1"/>
-        <v>Mohamed Fathy</v>
-      </c>
+      <c r="L33" s="57"/>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
     </row>
@@ -14102,10 +14081,7 @@
       <c r="K34" s="11">
         <v>2</v>
       </c>
-      <c r="L34" s="57" t="str">
-        <f t="shared" si="1"/>
-        <v>Iman Bahaa</v>
-      </c>
+      <c r="L34" s="57"/>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
@@ -14139,10 +14115,7 @@
       <c r="K35" s="11">
         <v>9</v>
       </c>
-      <c r="L35" s="57" t="str">
-        <f t="shared" si="1"/>
-        <v>Islam Gamal</v>
-      </c>
+      <c r="L35" s="57"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
@@ -14176,10 +14149,7 @@
       <c r="K36" s="11">
         <v>14</v>
       </c>
-      <c r="L36" s="57" t="str">
-        <f t="shared" si="1"/>
-        <v>Nasr Hassan</v>
-      </c>
+      <c r="L36" s="57"/>
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
@@ -14212,10 +14182,7 @@
       <c r="K37" s="11">
         <v>8</v>
       </c>
-      <c r="L37" s="57" t="str">
-        <f t="shared" si="1"/>
-        <v>Samah Fahmy</v>
-      </c>
+      <c r="L37" s="57"/>
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
@@ -14248,10 +14215,7 @@
       <c r="K38" s="11">
         <v>4</v>
       </c>
-      <c r="L38" s="57" t="str">
-        <f t="shared" si="1"/>
-        <v>Mohamed Mostafa</v>
-      </c>
+      <c r="L38" s="57"/>
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
     </row>
@@ -14284,10 +14248,7 @@
       <c r="K39" s="11">
         <v>1</v>
       </c>
-      <c r="L39" s="57" t="str">
-        <f t="shared" si="1"/>
-        <v>Mirna Tarek</v>
-      </c>
+      <c r="L39" s="57"/>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
     </row>
@@ -14320,10 +14281,7 @@
       <c r="K40" s="11">
         <v>3</v>
       </c>
-      <c r="L40" s="57" t="str">
-        <f t="shared" si="1"/>
-        <v>Ahmed Mohamed</v>
-      </c>
+      <c r="L40" s="57"/>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
     </row>
@@ -14356,10 +14314,7 @@
       <c r="K41" s="11">
         <v>13</v>
       </c>
-      <c r="L41" s="57" t="str">
-        <f t="shared" si="1"/>
-        <v>Hania Gomaa</v>
-      </c>
+      <c r="L41" s="57"/>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
     </row>
@@ -14601,7 +14556,7 @@
         <v>33666</v>
       </c>
       <c r="F55" s="62">
-        <f t="shared" ref="F55:F69" ca="1" si="2">DATEDIF(E55,TODAY(),"Y")</f>
+        <f t="shared" ref="F55:F69" ca="1" si="1">DATEDIF(E55,TODAY(),"Y")</f>
         <v>34</v>
       </c>
       <c r="G55" s="62" t="s">
@@ -14642,7 +14597,7 @@
         <v>33701</v>
       </c>
       <c r="F56" s="8">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>34</v>
       </c>
       <c r="G56" s="8" t="s">
@@ -14678,7 +14633,7 @@
         <v>32317</v>
       </c>
       <c r="F57" s="8">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>38</v>
       </c>
       <c r="G57" s="8" t="s">
@@ -14714,7 +14669,7 @@
         <v>27526</v>
       </c>
       <c r="F58" s="8">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>51</v>
       </c>
       <c r="G58" s="8" t="s">
@@ -14750,7 +14705,7 @@
         <v>29324</v>
       </c>
       <c r="F59" s="8">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>46</v>
       </c>
       <c r="G59" s="8" t="s">
@@ -14784,7 +14739,7 @@
         <v>20162</v>
       </c>
       <c r="F60" s="8">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>71</v>
       </c>
       <c r="G60" s="8" t="s">
@@ -14818,7 +14773,7 @@
         <v>23422</v>
       </c>
       <c r="F61" s="8">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>62</v>
       </c>
       <c r="G61" s="8" t="s">
@@ -14852,7 +14807,7 @@
         <v>23027</v>
       </c>
       <c r="F62" s="8">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>63</v>
       </c>
       <c r="G62" s="8" t="s">
@@ -14886,7 +14841,7 @@
         <v>24885</v>
       </c>
       <c r="F63" s="8">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>58</v>
       </c>
       <c r="G63" s="8" t="s">
@@ -14920,7 +14875,7 @@
         <v>22751</v>
       </c>
       <c r="F64" s="8">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>64</v>
       </c>
       <c r="G64" s="8" t="s">
@@ -14954,7 +14909,7 @@
         <v>24549</v>
       </c>
       <c r="F65" s="8">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>59</v>
       </c>
       <c r="G65" s="8" t="s">
@@ -14988,7 +14943,7 @@
         <v>26408</v>
       </c>
       <c r="F66" s="8">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>54</v>
       </c>
       <c r="G66" s="8" t="s">
@@ -15022,7 +14977,7 @@
         <v>29726</v>
       </c>
       <c r="F67" s="8">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>45</v>
       </c>
       <c r="G67" s="8" t="s">
@@ -15056,7 +15011,7 @@
         <v>23914</v>
       </c>
       <c r="F68" s="8">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>61</v>
       </c>
       <c r="G68" s="8" t="s">
@@ -15090,7 +15045,7 @@
         <v>27597</v>
       </c>
       <c r="F69" s="8">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="1"/>
         <v>51</v>
       </c>
       <c r="G69" s="8" t="s">

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2F6CCE-3AC4-47D7-86F8-961C9720A066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC22469-E24D-44F9-AF19-113C41DE76A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="D9" s="40">
         <f ca="1">NOW()</f>
-        <v>46294.123200810187</v>
+        <v>46294.124963773145</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="18" x14ac:dyDescent="0.35">
@@ -13837,7 +13837,10 @@
       <c r="K27" s="12">
         <v>15</v>
       </c>
-      <c r="L27" s="57"/>
+      <c r="L27" s="57" t="str">
+        <f>VLOOKUP(K27,$B$21:$I$46,2)</f>
+        <v>Rania Hassan</v>
+      </c>
       <c r="M27" s="6"/>
       <c r="N27" s="11" t="s">
         <v>10</v>
@@ -13873,7 +13876,10 @@
       <c r="K28" s="11">
         <v>10</v>
       </c>
-      <c r="L28" s="57"/>
+      <c r="L28" s="57" t="str">
+        <f t="shared" ref="L28:L41" si="1">VLOOKUP(K28,$B$21:$I$46,2)</f>
+        <v>Yousef Amr</v>
+      </c>
       <c r="M28" s="6"/>
       <c r="N28" s="11" t="s">
         <v>11</v>
@@ -13909,7 +13915,10 @@
       <c r="K29" s="11">
         <v>7</v>
       </c>
-      <c r="L29" s="57"/>
+      <c r="L29" s="57" t="str">
+        <f t="shared" si="1"/>
+        <v>Bakr Elmallwany</v>
+      </c>
       <c r="M29" s="6"/>
       <c r="N29" s="11" t="s">
         <v>12</v>
@@ -13945,7 +13954,10 @@
       <c r="K30" s="11">
         <v>11</v>
       </c>
-      <c r="L30" s="57"/>
+      <c r="L30" s="57" t="str">
+        <f t="shared" si="1"/>
+        <v>Omar Mohamed</v>
+      </c>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
     </row>
@@ -13979,7 +13991,10 @@
       <c r="K31" s="11">
         <v>5</v>
       </c>
-      <c r="L31" s="57"/>
+      <c r="L31" s="57" t="str">
+        <f t="shared" si="1"/>
+        <v>Hesham Mostafa</v>
+      </c>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
@@ -14013,7 +14028,10 @@
       <c r="K32" s="11">
         <v>6</v>
       </c>
-      <c r="L32" s="57"/>
+      <c r="L32" s="57" t="str">
+        <f t="shared" si="1"/>
+        <v>Ibrahim Ali</v>
+      </c>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
     </row>
@@ -14047,7 +14065,10 @@
       <c r="K33" s="11">
         <v>12</v>
       </c>
-      <c r="L33" s="57"/>
+      <c r="L33" s="57" t="str">
+        <f t="shared" si="1"/>
+        <v>Mohamed Fathy</v>
+      </c>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
     </row>
@@ -14081,7 +14102,10 @@
       <c r="K34" s="11">
         <v>2</v>
       </c>
-      <c r="L34" s="57"/>
+      <c r="L34" s="57" t="str">
+        <f t="shared" si="1"/>
+        <v>Iman Bahaa</v>
+      </c>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
@@ -14115,7 +14139,10 @@
       <c r="K35" s="11">
         <v>9</v>
       </c>
-      <c r="L35" s="57"/>
+      <c r="L35" s="57" t="str">
+        <f t="shared" si="1"/>
+        <v>Islam Gamal</v>
+      </c>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
@@ -14149,7 +14176,10 @@
       <c r="K36" s="11">
         <v>14</v>
       </c>
-      <c r="L36" s="57"/>
+      <c r="L36" s="57" t="str">
+        <f t="shared" si="1"/>
+        <v>Nasr Hassan</v>
+      </c>
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
@@ -14182,7 +14212,10 @@
       <c r="K37" s="11">
         <v>8</v>
       </c>
-      <c r="L37" s="57"/>
+      <c r="L37" s="57" t="str">
+        <f t="shared" si="1"/>
+        <v>Samah Fahmy</v>
+      </c>
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
@@ -14215,7 +14248,10 @@
       <c r="K38" s="11">
         <v>4</v>
       </c>
-      <c r="L38" s="57"/>
+      <c r="L38" s="57" t="str">
+        <f t="shared" si="1"/>
+        <v>Mohamed Mostafa</v>
+      </c>
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
     </row>
@@ -14248,7 +14284,10 @@
       <c r="K39" s="11">
         <v>1</v>
       </c>
-      <c r="L39" s="57"/>
+      <c r="L39" s="57" t="str">
+        <f t="shared" si="1"/>
+        <v>Mirna Tarek</v>
+      </c>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
     </row>
@@ -14281,7 +14320,10 @@
       <c r="K40" s="11">
         <v>3</v>
       </c>
-      <c r="L40" s="57"/>
+      <c r="L40" s="57" t="str">
+        <f t="shared" si="1"/>
+        <v>Ahmed Mohamed</v>
+      </c>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
     </row>
@@ -14314,7 +14356,10 @@
       <c r="K41" s="11">
         <v>13</v>
       </c>
-      <c r="L41" s="57"/>
+      <c r="L41" s="57" t="str">
+        <f t="shared" si="1"/>
+        <v>Hania Gomaa</v>
+      </c>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
     </row>
@@ -14556,7 +14601,7 @@
         <v>33666</v>
       </c>
       <c r="F55" s="62">
-        <f t="shared" ref="F55:F69" ca="1" si="1">DATEDIF(E55,TODAY(),"Y")</f>
+        <f t="shared" ref="F55:F69" ca="1" si="2">DATEDIF(E55,TODAY(),"Y")</f>
         <v>34</v>
       </c>
       <c r="G55" s="62" t="s">
@@ -14597,7 +14642,7 @@
         <v>33701</v>
       </c>
       <c r="F56" s="8">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>34</v>
       </c>
       <c r="G56" s="8" t="s">
@@ -14633,7 +14678,7 @@
         <v>32317</v>
       </c>
       <c r="F57" s="8">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>38</v>
       </c>
       <c r="G57" s="8" t="s">
@@ -14669,7 +14714,7 @@
         <v>27526</v>
       </c>
       <c r="F58" s="8">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>51</v>
       </c>
       <c r="G58" s="8" t="s">
@@ -14705,7 +14750,7 @@
         <v>29324</v>
       </c>
       <c r="F59" s="8">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>46</v>
       </c>
       <c r="G59" s="8" t="s">
@@ -14739,7 +14784,7 @@
         <v>20162</v>
       </c>
       <c r="F60" s="8">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>71</v>
       </c>
       <c r="G60" s="8" t="s">
@@ -14773,7 +14818,7 @@
         <v>23422</v>
       </c>
       <c r="F61" s="8">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>62</v>
       </c>
       <c r="G61" s="8" t="s">
@@ -14807,7 +14852,7 @@
         <v>23027</v>
       </c>
       <c r="F62" s="8">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>63</v>
       </c>
       <c r="G62" s="8" t="s">
@@ -14841,7 +14886,7 @@
         <v>24885</v>
       </c>
       <c r="F63" s="8">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>58</v>
       </c>
       <c r="G63" s="8" t="s">
@@ -14875,7 +14920,7 @@
         <v>22751</v>
       </c>
       <c r="F64" s="8">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>64</v>
       </c>
       <c r="G64" s="8" t="s">
@@ -14909,7 +14954,7 @@
         <v>24549</v>
       </c>
       <c r="F65" s="8">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>59</v>
       </c>
       <c r="G65" s="8" t="s">
@@ -14943,7 +14988,7 @@
         <v>26408</v>
       </c>
       <c r="F66" s="8">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>54</v>
       </c>
       <c r="G66" s="8" t="s">
@@ -14977,7 +15022,7 @@
         <v>29726</v>
       </c>
       <c r="F67" s="8">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>45</v>
       </c>
       <c r="G67" s="8" t="s">
@@ -15011,7 +15056,7 @@
         <v>23914</v>
       </c>
       <c r="F68" s="8">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>61</v>
       </c>
       <c r="G68" s="8" t="s">
@@ -15045,7 +15090,7 @@
         <v>27597</v>
       </c>
       <c r="F69" s="8">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>51</v>
       </c>
       <c r="G69" s="8" t="s">

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC22469-E24D-44F9-AF19-113C41DE76A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5245FE-E78D-40D4-90D0-22BDB39704B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Date and Time " sheetId="19" r:id="rId1"/>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="D9" s="40">
         <f ca="1">NOW()</f>
-        <v>46294.124963773145</v>
+        <v>46294.133346296294</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="18" x14ac:dyDescent="0.35">
@@ -14658,7 +14658,10 @@
       <c r="K56" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="L56" s="57"/>
+      <c r="L56" s="57" t="str">
+        <f>VLOOKUP(K56,C54:I79,5,FALSE)</f>
+        <v>Female</v>
+      </c>
       <c r="M56" s="6"/>
       <c r="N56" s="11" t="s">
         <v>11</v>
@@ -14694,7 +14697,10 @@
       <c r="K57" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="L57" s="57"/>
+      <c r="L57" s="57" t="str">
+        <f t="shared" ref="L57:L70" si="3">VLOOKUP(K57,C55:I80,5,FALSE)</f>
+        <v>Female</v>
+      </c>
       <c r="M57" s="6"/>
       <c r="N57" s="11" t="s">
         <v>10</v>
@@ -14730,7 +14736,10 @@
       <c r="K58" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L58" s="57"/>
+      <c r="L58" s="57" t="str">
+        <f t="shared" si="3"/>
+        <v>Male</v>
+      </c>
       <c r="M58" s="6"/>
       <c r="N58" s="11" t="s">
         <v>6</v>
@@ -14766,7 +14775,10 @@
       <c r="K59" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="L59" s="57"/>
+      <c r="L59" s="57" t="str">
+        <f t="shared" si="3"/>
+        <v>Male</v>
+      </c>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
@@ -14800,7 +14812,10 @@
       <c r="K60" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="L60" s="57"/>
+      <c r="L60" s="57" t="str">
+        <f t="shared" si="3"/>
+        <v>Male</v>
+      </c>
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
     </row>
@@ -14834,7 +14849,10 @@
       <c r="K61" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L61" s="57"/>
+      <c r="L61" s="57" t="str">
+        <f t="shared" si="3"/>
+        <v>Male</v>
+      </c>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
     </row>
@@ -14868,7 +14886,10 @@
       <c r="K62" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="L62" s="57"/>
+      <c r="L62" s="57" t="str">
+        <f t="shared" si="3"/>
+        <v>Male</v>
+      </c>
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
     </row>
@@ -14902,7 +14923,10 @@
       <c r="K63" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="L63" s="57"/>
+      <c r="L63" s="57" t="str">
+        <f t="shared" si="3"/>
+        <v>Female</v>
+      </c>
       <c r="M63" s="6"/>
       <c r="N63" s="6"/>
     </row>
@@ -14936,7 +14960,10 @@
       <c r="K64" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="L64" s="57"/>
+      <c r="L64" s="57" t="str">
+        <f t="shared" si="3"/>
+        <v>Male</v>
+      </c>
       <c r="M64" s="6"/>
       <c r="N64" s="6"/>
     </row>
@@ -14970,7 +14997,10 @@
       <c r="K65" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="L65" s="57"/>
+      <c r="L65" s="57" t="str">
+        <f t="shared" si="3"/>
+        <v>Male</v>
+      </c>
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
     </row>
@@ -15004,7 +15034,10 @@
       <c r="K66" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="L66" s="57"/>
+      <c r="L66" s="57" t="str">
+        <f t="shared" si="3"/>
+        <v>Male</v>
+      </c>
       <c r="M66" s="6"/>
       <c r="N66" s="6"/>
     </row>
@@ -15038,7 +15071,10 @@
       <c r="K67" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L67" s="57"/>
+      <c r="L67" s="57" t="str">
+        <f t="shared" si="3"/>
+        <v>Male</v>
+      </c>
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
     </row>
@@ -15072,7 +15108,10 @@
       <c r="K68" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="L68" s="57"/>
+      <c r="L68" s="57" t="str">
+        <f t="shared" si="3"/>
+        <v>Female</v>
+      </c>
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
     </row>
@@ -15106,7 +15145,10 @@
       <c r="K69" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="L69" s="57"/>
+      <c r="L69" s="57" t="str">
+        <f t="shared" si="3"/>
+        <v>Male</v>
+      </c>
       <c r="M69" s="6"/>
       <c r="N69" s="6"/>
     </row>
@@ -15139,7 +15181,10 @@
       <c r="K70" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L70" s="57"/>
+      <c r="L70" s="57" t="str">
+        <f t="shared" si="3"/>
+        <v>Male</v>
+      </c>
       <c r="M70" s="6"/>
       <c r="N70" s="6"/>
     </row>
@@ -15872,11 +15917,11 @@
         <v>6</v>
       </c>
       <c r="B18" s="24" t="str">
-        <f>HLOOKUP(B17,$A$3:$K$10,2,FALSE)</f>
+        <f>HLOOKUP(B17,$A$3:$K$10,2)</f>
         <v>Iman Bahaa</v>
       </c>
       <c r="C18" s="24" t="str">
-        <f t="shared" ref="C18:K18" si="1">HLOOKUP(C17,$A$3:$K$10,2,FALSE)</f>
+        <f t="shared" ref="C18:K18" si="1">HLOOKUP(C17,$A$3:$K$10,2)</f>
         <v>Islam Gamal</v>
       </c>
       <c r="D18" s="24" t="str">
@@ -17068,7 +17113,7 @@
         <v>15</v>
       </c>
       <c r="K22" s="26" t="str">
-        <f>_xlfn.XLOOKUP(J22,$D$3:$D$28,$A$3:$A$28,"مش موجود",0,1)</f>
+        <f>_xlfn.XLOOKUP(J22,$D$3:$D$28,$A$3:$A$28)</f>
         <v>Sayed Gohar</v>
       </c>
       <c r="L22" s="11" t="s">
@@ -17104,7 +17149,7 @@
         <v>10</v>
       </c>
       <c r="K23" s="26" t="str">
-        <f t="shared" ref="K23:K27" si="1">_xlfn.XLOOKUP(J23,$D$3:$D$28,$A$3:$A$28,"مش موجود",0,1)</f>
+        <f t="shared" ref="K23:K27" si="1">_xlfn.XLOOKUP(J23,$D$3:$D$28,$A$3:$A$28)</f>
         <v>Yousef Amr</v>
       </c>
       <c r="L23" s="11" t="s">
@@ -17238,9 +17283,9 @@
       <c r="J27" s="11">
         <v>265</v>
       </c>
-      <c r="K27" s="26" t="str">
+      <c r="K27" s="26" t="e">
         <f t="shared" si="1"/>
-        <v>مش موجود</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -17922,10 +17967,7 @@
       <c r="J54" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="K54" s="26" t="str">
-        <f>_xlfn.XLOOKUP(J54,$A$35:$A$60,$G$35:$G$60,"مش موجود",0,1 )</f>
-        <v>Trading</v>
-      </c>
+      <c r="K54" s="26"/>
       <c r="L54" s="11" t="s">
         <v>10</v>
       </c>
@@ -17958,10 +18000,7 @@
       <c r="J55" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="K55" s="26" t="str">
-        <f t="shared" ref="K55:K59" si="3">_xlfn.XLOOKUP(J55,$A$35:$A$60,$G$35:$G$60,"مش موجود",0,1 )</f>
-        <v>Oil &amp; Gas</v>
-      </c>
+      <c r="K55" s="26"/>
       <c r="L55" s="11" t="s">
         <v>11</v>
       </c>
@@ -17994,10 +18033,7 @@
       <c r="J56" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>Trading</v>
-      </c>
+      <c r="K56" s="26"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
@@ -18027,10 +18063,7 @@
       <c r="J57" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="K57" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>Trading</v>
-      </c>
+      <c r="K57" s="26"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
@@ -18060,10 +18093,7 @@
       <c r="J58" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="K58" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>Manufacturing</v>
-      </c>
+      <c r="K58" s="26"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
@@ -18093,10 +18123,7 @@
       <c r="J59" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="K59" s="66" t="str">
-        <f t="shared" si="3"/>
-        <v>مش موجود</v>
-      </c>
+      <c r="K59" s="66"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5245FE-E78D-40D4-90D0-22BDB39704B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4046336D-8AF3-4ECB-B400-063B4838F902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="871" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Date and Time " sheetId="19" r:id="rId1"/>
@@ -767,7 +767,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]mmmmm;@"/>
     <numFmt numFmtId="166" formatCode="yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -983,14 +983,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <i/>
-      <sz val="12"/>
-      <color theme="1" tint="4.9989318521683403E-2"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -1035,7 +1027,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1154,12 +1146,6 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FF70AD47"/>
       </patternFill>
     </fill>
     <fill>
@@ -1392,7 +1378,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1573,14 +1559,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1598,10 +1581,10 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1613,16 +1596,16 @@
     <xf numFmtId="0" fontId="18" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1634,7 +1617,7 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1679,13 +1662,13 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -12319,7 +12302,7 @@
       <c r="C8" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="D8" s="72">
+      <c r="D8" s="71">
         <f ca="1">TODAY()</f>
         <v>46294</v>
       </c>
@@ -12336,7 +12319,7 @@
       </c>
       <c r="D9" s="40">
         <f ca="1">NOW()</f>
-        <v>46294.133346296294</v>
+        <v>46294.138641319441</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="18" x14ac:dyDescent="0.35">
@@ -12353,7 +12336,7 @@
       <c r="F12" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="G12" s="71"/>
+      <c r="G12" s="70"/>
     </row>
     <row r="13" spans="2:7" ht="18" x14ac:dyDescent="0.35">
       <c r="B13" s="39" t="s">
@@ -12486,26 +12469,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="1" customFormat="1" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="88" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="89"/>
-      <c r="L1" s="89"/>
-      <c r="M1" s="89"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="89"/>
-      <c r="P1" s="89"/>
-      <c r="Q1" s="89"/>
-      <c r="R1" s="89"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
+      <c r="R1" s="88"/>
     </row>
     <row r="3" spans="1:18" ht="23.4" x14ac:dyDescent="0.3">
       <c r="B3" s="48" t="s">
@@ -12555,10 +12538,10 @@
       <c r="M26" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="O26" s="87" t="s">
+      <c r="O26" s="86" t="s">
         <v>87</v>
       </c>
-      <c r="P26" s="88"/>
+      <c r="P26" s="87"/>
     </row>
     <row r="27" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
@@ -13284,40 +13267,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="98" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
     </row>
     <row r="3" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B3" s="95" t="s">
+      <c r="B3" s="94" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="G3" s="95" t="s">
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="G3" s="94" t="s">
         <v>78</v>
       </c>
-      <c r="H3" s="95"/>
-      <c r="I3" s="95"/>
-      <c r="J3" s="95"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="G4" s="17">
@@ -13540,48 +13523,48 @@
       <c r="C14" s="21"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="K16" s="101" t="s">
+      <c r="K16" s="100" t="s">
         <v>174</v>
       </c>
-      <c r="M16" s="100" t="s">
+      <c r="M16" s="99" t="s">
         <v>175</v>
       </c>
-      <c r="N16" s="100"/>
-      <c r="O16" s="100"/>
-      <c r="P16" s="100"/>
-      <c r="Q16" s="100"/>
+      <c r="N16" s="99"/>
+      <c r="O16" s="99"/>
+      <c r="P16" s="99"/>
+      <c r="Q16" s="99"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="K17" s="101"/>
-      <c r="M17" s="100"/>
-      <c r="N17" s="100"/>
-      <c r="O17" s="100"/>
-      <c r="P17" s="100"/>
-      <c r="Q17" s="100"/>
+      <c r="K17" s="100"/>
+      <c r="M17" s="99"/>
+      <c r="N17" s="99"/>
+      <c r="O17" s="99"/>
+      <c r="P17" s="99"/>
+      <c r="Q17" s="99"/>
     </row>
     <row r="19" spans="2:17" ht="21" x14ac:dyDescent="0.3">
-      <c r="B19" s="96" t="s">
+      <c r="B19" s="95" t="s">
         <v>154</v>
       </c>
-      <c r="C19" s="97"/>
-      <c r="D19" s="97"/>
-      <c r="E19" s="97"/>
-      <c r="F19" s="97"/>
-      <c r="G19" s="97"/>
-      <c r="H19" s="97"/>
-      <c r="I19" s="98"/>
+      <c r="C19" s="96"/>
+      <c r="D19" s="96"/>
+      <c r="E19" s="96"/>
+      <c r="F19" s="96"/>
+      <c r="G19" s="96"/>
+      <c r="H19" s="96"/>
+      <c r="I19" s="97"/>
       <c r="J19" s="6"/>
       <c r="K19" s="61" t="s">
         <v>4</v>
       </c>
       <c r="L19" s="6"/>
-      <c r="M19" s="93" t="s">
+      <c r="M19" s="92" t="s">
         <v>156</v>
       </c>
-      <c r="N19" s="93"/>
-      <c r="O19" s="93"/>
-      <c r="P19" s="93"/>
-      <c r="Q19" s="93"/>
+      <c r="N19" s="92"/>
+      <c r="O19" s="92"/>
+      <c r="P19" s="92"/>
+      <c r="Q19" s="92"/>
     </row>
     <row r="20" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B20" s="6"/>
@@ -13596,13 +13579,13 @@
       <c r="K20" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="94" t="s">
+      <c r="M20" s="93" t="s">
         <v>157</v>
       </c>
-      <c r="N20" s="94"/>
-      <c r="O20" s="94"/>
-      <c r="P20" s="94"/>
-      <c r="Q20" s="94"/>
+      <c r="N20" s="93"/>
+      <c r="O20" s="93"/>
+      <c r="P20" s="93"/>
+      <c r="Q20" s="93"/>
     </row>
     <row r="21" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B21" s="27" t="s">
@@ -13633,13 +13616,13 @@
       <c r="K21" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="M21" s="93" t="s">
+      <c r="M21" s="92" t="s">
         <v>158</v>
       </c>
-      <c r="N21" s="93"/>
-      <c r="O21" s="93"/>
-      <c r="P21" s="93"/>
-      <c r="Q21" s="93"/>
+      <c r="N21" s="92"/>
+      <c r="O21" s="92"/>
+      <c r="P21" s="92"/>
+      <c r="Q21" s="92"/>
     </row>
     <row r="22" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B22" s="62">
@@ -13671,13 +13654,13 @@
       <c r="K22" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="M22" s="94" t="s">
+      <c r="M22" s="93" t="s">
         <v>160</v>
       </c>
-      <c r="N22" s="94"/>
-      <c r="O22" s="94"/>
-      <c r="P22" s="94"/>
-      <c r="Q22" s="94"/>
+      <c r="N22" s="93"/>
+      <c r="O22" s="93"/>
+      <c r="P22" s="93"/>
+      <c r="Q22" s="93"/>
     </row>
     <row r="23" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B23" s="8">
@@ -14443,15 +14426,15 @@
         <v>78956</v>
       </c>
       <c r="J44" s="6"/>
-      <c r="K44" s="90" t="s">
+      <c r="K44" s="89" t="s">
         <v>176</v>
       </c>
-      <c r="L44" s="90"/>
-      <c r="M44" s="90"/>
-      <c r="N44" s="90"/>
-      <c r="O44" s="90"/>
-      <c r="P44" s="90"/>
-      <c r="Q44" s="90"/>
+      <c r="L44" s="89"/>
+      <c r="M44" s="89"/>
+      <c r="N44" s="89"/>
+      <c r="O44" s="89"/>
+      <c r="P44" s="89"/>
+      <c r="Q44" s="89"/>
     </row>
     <row r="45" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B45" s="8">
@@ -14479,15 +14462,15 @@
         <v>83000</v>
       </c>
       <c r="J45" s="6"/>
-      <c r="K45" s="91" t="s">
+      <c r="K45" s="90" t="s">
         <v>159</v>
       </c>
-      <c r="L45" s="91"/>
-      <c r="M45" s="91"/>
-      <c r="N45" s="91"/>
-      <c r="O45" s="91"/>
-      <c r="P45" s="91"/>
-      <c r="Q45" s="91"/>
+      <c r="L45" s="90"/>
+      <c r="M45" s="90"/>
+      <c r="N45" s="90"/>
+      <c r="O45" s="90"/>
+      <c r="P45" s="90"/>
+      <c r="Q45" s="90"/>
     </row>
     <row r="46" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B46" s="8">
@@ -14515,15 +14498,15 @@
         <v>85000</v>
       </c>
       <c r="J46" s="6"/>
-      <c r="K46" s="90" t="s">
+      <c r="K46" s="89" t="s">
         <v>177</v>
       </c>
-      <c r="L46" s="90"/>
-      <c r="M46" s="90"/>
-      <c r="N46" s="90"/>
-      <c r="O46" s="90"/>
-      <c r="P46" s="90"/>
-      <c r="Q46" s="90"/>
+      <c r="L46" s="89"/>
+      <c r="M46" s="89"/>
+      <c r="N46" s="89"/>
+      <c r="O46" s="89"/>
+      <c r="P46" s="89"/>
+      <c r="Q46" s="89"/>
     </row>
     <row r="47" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
@@ -14538,18 +14521,18 @@
       <c r="J47" s="6"/>
     </row>
     <row r="50" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="H50" s="92" t="s">
+      <c r="H50" s="91" t="s">
         <v>178</v>
       </c>
-      <c r="I50" s="92"/>
-      <c r="J50" s="92"/>
-      <c r="K50" s="92"/>
+      <c r="I50" s="91"/>
+      <c r="J50" s="91"/>
+      <c r="K50" s="91"/>
     </row>
     <row r="51" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="H51" s="92"/>
-      <c r="I51" s="92"/>
-      <c r="J51" s="92"/>
-      <c r="K51" s="92"/>
+      <c r="H51" s="91"/>
+      <c r="I51" s="91"/>
+      <c r="J51" s="91"/>
+      <c r="K51" s="91"/>
     </row>
     <row r="54" spans="2:17" ht="18" x14ac:dyDescent="0.3">
       <c r="B54" s="27" t="s">
@@ -15295,15 +15278,15 @@
         <v>85000</v>
       </c>
       <c r="J74" s="6"/>
-      <c r="K74" s="90" t="s">
+      <c r="K74" s="89" t="s">
         <v>176</v>
       </c>
-      <c r="L74" s="90"/>
-      <c r="M74" s="90"/>
-      <c r="N74" s="90"/>
-      <c r="O74" s="90"/>
-      <c r="P74" s="90"/>
-      <c r="Q74" s="90"/>
+      <c r="L74" s="89"/>
+      <c r="M74" s="89"/>
+      <c r="N74" s="89"/>
+      <c r="O74" s="89"/>
+      <c r="P74" s="89"/>
+      <c r="Q74" s="89"/>
     </row>
     <row r="75" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B75" s="8">
@@ -15331,15 +15314,15 @@
         <v>77100</v>
       </c>
       <c r="J75" s="6"/>
-      <c r="K75" s="91" t="s">
+      <c r="K75" s="90" t="s">
         <v>159</v>
       </c>
-      <c r="L75" s="91"/>
-      <c r="M75" s="91"/>
-      <c r="N75" s="91"/>
-      <c r="O75" s="91"/>
-      <c r="P75" s="91"/>
-      <c r="Q75" s="91"/>
+      <c r="L75" s="90"/>
+      <c r="M75" s="90"/>
+      <c r="N75" s="90"/>
+      <c r="O75" s="90"/>
+      <c r="P75" s="90"/>
+      <c r="Q75" s="90"/>
     </row>
     <row r="76" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B76" s="8">
@@ -15367,15 +15350,15 @@
         <v>110000</v>
       </c>
       <c r="J76" s="6"/>
-      <c r="K76" s="90" t="s">
+      <c r="K76" s="89" t="s">
         <v>177</v>
       </c>
-      <c r="L76" s="90"/>
-      <c r="M76" s="90"/>
-      <c r="N76" s="90"/>
-      <c r="O76" s="90"/>
-      <c r="P76" s="90"/>
-      <c r="Q76" s="90"/>
+      <c r="L76" s="89"/>
+      <c r="M76" s="89"/>
+      <c r="N76" s="89"/>
+      <c r="O76" s="89"/>
+      <c r="P76" s="89"/>
+      <c r="Q76" s="89"/>
     </row>
     <row r="77" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B77" s="8">
@@ -15430,15 +15413,15 @@
         <v>83000</v>
       </c>
       <c r="J78" s="6"/>
-      <c r="K78" s="90" t="s">
+      <c r="K78" s="89" t="s">
         <v>179</v>
       </c>
-      <c r="L78" s="90"/>
-      <c r="M78" s="90"/>
-      <c r="N78" s="90"/>
-      <c r="O78" s="90"/>
-      <c r="P78" s="90"/>
-      <c r="Q78" s="90"/>
+      <c r="L78" s="89"/>
+      <c r="M78" s="89"/>
+      <c r="N78" s="89"/>
+      <c r="O78" s="89"/>
+      <c r="P78" s="89"/>
+      <c r="Q78" s="89"/>
     </row>
     <row r="79" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B79" s="8">
@@ -15510,21 +15493,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="102" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
     </row>
     <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
@@ -15958,50 +15941,50 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="18" x14ac:dyDescent="0.3">
-      <c r="H21" s="102" t="s">
+      <c r="H21" s="101" t="s">
         <v>161</v>
       </c>
-      <c r="I21" s="102"/>
-      <c r="J21" s="102"/>
-      <c r="K21" s="102"/>
+      <c r="I21" s="101"/>
+      <c r="J21" s="101"/>
+      <c r="K21" s="101"/>
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.3">
-      <c r="H22" s="102" t="s">
+      <c r="H22" s="101" t="s">
         <v>162</v>
       </c>
-      <c r="I22" s="102"/>
-      <c r="J22" s="102"/>
-      <c r="K22" s="102"/>
+      <c r="I22" s="101"/>
+      <c r="J22" s="101"/>
+      <c r="K22" s="101"/>
     </row>
     <row r="23" spans="1:11" ht="18" x14ac:dyDescent="0.3">
-      <c r="H23" s="102" t="s">
+      <c r="H23" s="101" t="s">
         <v>163</v>
       </c>
-      <c r="I23" s="102"/>
-      <c r="J23" s="102"/>
-      <c r="K23" s="102"/>
+      <c r="I23" s="101"/>
+      <c r="J23" s="101"/>
+      <c r="K23" s="101"/>
     </row>
     <row r="24" spans="1:11" ht="18" x14ac:dyDescent="0.3">
-      <c r="H24" s="102" t="s">
+      <c r="H24" s="101" t="s">
         <v>164</v>
       </c>
-      <c r="I24" s="102"/>
-      <c r="J24" s="102"/>
-      <c r="K24" s="102"/>
+      <c r="I24" s="101"/>
+      <c r="J24" s="101"/>
+      <c r="K24" s="101"/>
     </row>
     <row r="28" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E28" s="92" t="s">
+      <c r="E28" s="91" t="s">
         <v>178</v>
       </c>
-      <c r="F28" s="92"/>
-      <c r="G28" s="92"/>
-      <c r="H28" s="92"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="91"/>
+      <c r="H28" s="91"/>
     </row>
     <row r="29" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E29" s="92"/>
-      <c r="F29" s="92"/>
-      <c r="G29" s="92"/>
-      <c r="H29" s="92"/>
+      <c r="E29" s="91"/>
+      <c r="F29" s="91"/>
+      <c r="G29" s="91"/>
+      <c r="H29" s="91"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
@@ -16445,27 +16428,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
         <v>204</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
     </row>
     <row r="3" spans="1:19" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
@@ -16492,17 +16475,17 @@
       <c r="H3" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="81" t="s">
+      <c r="J3" s="80" t="s">
         <v>166</v>
       </c>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
-      <c r="O3" s="81"/>
-      <c r="P3" s="81"/>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="81"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
@@ -16557,17 +16540,17 @@
       <c r="H5" s="8">
         <v>64000</v>
       </c>
-      <c r="J5" s="80" t="s">
+      <c r="J5" s="79" t="s">
         <v>167</v>
       </c>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="80"/>
-      <c r="O5" s="80"/>
-      <c r="P5" s="80"/>
-      <c r="Q5" s="80"/>
-      <c r="R5" s="80"/>
+      <c r="K5" s="79"/>
+      <c r="L5" s="79"/>
+      <c r="M5" s="79"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
@@ -16625,15 +16608,15 @@
       <c r="J7" s="65" t="s">
         <v>168</v>
       </c>
-      <c r="L7" s="73" t="s">
+      <c r="L7" s="72" t="s">
         <v>180</v>
       </c>
-      <c r="M7" s="74"/>
-      <c r="N7" s="74"/>
-      <c r="O7" s="74"/>
-      <c r="P7" s="74"/>
-      <c r="Q7" s="74"/>
-      <c r="R7" s="74"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="73"/>
+      <c r="O7" s="73"/>
+      <c r="P7" s="73"/>
+      <c r="Q7" s="73"/>
+      <c r="R7" s="73"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
@@ -16691,15 +16674,15 @@
       <c r="J9" s="65" t="s">
         <v>169</v>
       </c>
-      <c r="L9" s="74" t="s">
+      <c r="L9" s="73" t="s">
         <v>184</v>
       </c>
-      <c r="M9" s="74"/>
-      <c r="N9" s="74"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="74"/>
-      <c r="Q9" s="74"/>
-      <c r="R9" s="74"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="73"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="73"/>
+      <c r="Q9" s="73"/>
+      <c r="R9" s="73"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
@@ -16757,15 +16740,15 @@
       <c r="J11" s="65" t="s">
         <v>170</v>
       </c>
-      <c r="L11" s="73" t="s">
+      <c r="L11" s="72" t="s">
         <v>185</v>
       </c>
-      <c r="M11" s="74"/>
-      <c r="N11" s="74"/>
-      <c r="O11" s="74"/>
-      <c r="P11" s="74"/>
-      <c r="Q11" s="74"/>
-      <c r="R11" s="74"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="73"/>
+      <c r="O11" s="73"/>
+      <c r="P11" s="73"/>
+      <c r="Q11" s="73"/>
+      <c r="R11" s="73"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
@@ -16823,15 +16806,15 @@
       <c r="J13" s="65" t="s">
         <v>171</v>
       </c>
-      <c r="L13" s="73" t="s">
+      <c r="L13" s="72" t="s">
         <v>181</v>
       </c>
-      <c r="M13" s="74"/>
-      <c r="N13" s="74"/>
-      <c r="O13" s="74"/>
-      <c r="P13" s="74"/>
-      <c r="Q13" s="74"/>
-      <c r="R13" s="74"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="73"/>
+      <c r="O13" s="73"/>
+      <c r="P13" s="73"/>
+      <c r="Q13" s="73"/>
+      <c r="R13" s="73"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
@@ -16889,15 +16872,15 @@
       <c r="J15" s="65" t="s">
         <v>172</v>
       </c>
-      <c r="L15" s="73" t="s">
+      <c r="L15" s="72" t="s">
         <v>182</v>
       </c>
-      <c r="M15" s="74"/>
-      <c r="N15" s="74"/>
-      <c r="O15" s="74"/>
-      <c r="P15" s="74"/>
-      <c r="Q15" s="74"/>
-      <c r="R15" s="74"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="73"/>
+      <c r="O15" s="73"/>
+      <c r="P15" s="73"/>
+      <c r="Q15" s="73"/>
+      <c r="R15" s="73"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
@@ -16955,15 +16938,15 @@
       <c r="J17" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="L17" s="73" t="s">
+      <c r="L17" s="72" t="s">
         <v>183</v>
       </c>
-      <c r="M17" s="74"/>
-      <c r="N17" s="74"/>
-      <c r="O17" s="74"/>
-      <c r="P17" s="74"/>
-      <c r="Q17" s="74"/>
-      <c r="R17" s="74"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="73"/>
+      <c r="O17" s="73"/>
+      <c r="P17" s="73"/>
+      <c r="Q17" s="73"/>
+      <c r="R17" s="73"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
@@ -17043,11 +17026,11 @@
       <c r="H20" s="8">
         <v>221850</v>
       </c>
-      <c r="J20" s="75" t="s">
+      <c r="J20" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="K20" s="76"/>
-      <c r="L20" s="76"/>
+      <c r="K20" s="75"/>
+      <c r="L20" s="75"/>
     </row>
     <row r="21" spans="1:18" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
@@ -17315,12 +17298,12 @@
       </c>
     </row>
     <row r="33" spans="1:18" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="H33" s="86" t="s">
+      <c r="H33" s="85" t="s">
         <v>186</v>
       </c>
-      <c r="I33" s="86"/>
-      <c r="J33" s="86"/>
-      <c r="K33" s="86"/>
+      <c r="I33" s="85"/>
+      <c r="J33" s="85"/>
+      <c r="K33" s="85"/>
     </row>
     <row r="35" spans="1:18" ht="18" x14ac:dyDescent="0.3">
       <c r="A35" s="27" t="s">
@@ -17347,17 +17330,17 @@
       <c r="H35" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="J35" s="81" t="s">
+      <c r="J35" s="80" t="s">
         <v>166</v>
       </c>
-      <c r="K35" s="81"/>
-      <c r="L35" s="81"/>
-      <c r="M35" s="81"/>
-      <c r="N35" s="81"/>
-      <c r="O35" s="81"/>
-      <c r="P35" s="81"/>
-      <c r="Q35" s="81"/>
-      <c r="R35" s="81"/>
+      <c r="K35" s="80"/>
+      <c r="L35" s="80"/>
+      <c r="M35" s="80"/>
+      <c r="N35" s="80"/>
+      <c r="O35" s="80"/>
+      <c r="P35" s="80"/>
+      <c r="Q35" s="80"/>
+      <c r="R35" s="80"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
@@ -17412,17 +17395,17 @@
       <c r="H37" s="8">
         <v>64000</v>
       </c>
-      <c r="J37" s="80" t="s">
+      <c r="J37" s="79" t="s">
         <v>167</v>
       </c>
-      <c r="K37" s="80"/>
-      <c r="L37" s="80"/>
-      <c r="M37" s="80"/>
-      <c r="N37" s="80"/>
-      <c r="O37" s="80"/>
-      <c r="P37" s="80"/>
-      <c r="Q37" s="80"/>
-      <c r="R37" s="80"/>
+      <c r="K37" s="79"/>
+      <c r="L37" s="79"/>
+      <c r="M37" s="79"/>
+      <c r="N37" s="79"/>
+      <c r="O37" s="79"/>
+      <c r="P37" s="79"/>
+      <c r="Q37" s="79"/>
+      <c r="R37" s="79"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
@@ -17480,15 +17463,15 @@
       <c r="J39" s="65" t="s">
         <v>168</v>
       </c>
-      <c r="L39" s="73" t="s">
+      <c r="L39" s="72" t="s">
         <v>180</v>
       </c>
-      <c r="M39" s="74"/>
-      <c r="N39" s="74"/>
-      <c r="O39" s="74"/>
-      <c r="P39" s="74"/>
-      <c r="Q39" s="74"/>
-      <c r="R39" s="74"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="73"/>
+      <c r="O39" s="73"/>
+      <c r="P39" s="73"/>
+      <c r="Q39" s="73"/>
+      <c r="R39" s="73"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
@@ -17546,15 +17529,15 @@
       <c r="J41" s="65" t="s">
         <v>169</v>
       </c>
-      <c r="L41" s="74" t="s">
+      <c r="L41" s="73" t="s">
         <v>184</v>
       </c>
-      <c r="M41" s="74"/>
-      <c r="N41" s="74"/>
-      <c r="O41" s="74"/>
-      <c r="P41" s="74"/>
-      <c r="Q41" s="74"/>
-      <c r="R41" s="74"/>
+      <c r="M41" s="73"/>
+      <c r="N41" s="73"/>
+      <c r="O41" s="73"/>
+      <c r="P41" s="73"/>
+      <c r="Q41" s="73"/>
+      <c r="R41" s="73"/>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
@@ -17612,15 +17595,15 @@
       <c r="J43" s="65" t="s">
         <v>170</v>
       </c>
-      <c r="L43" s="73" t="s">
+      <c r="L43" s="72" t="s">
         <v>185</v>
       </c>
-      <c r="M43" s="74"/>
-      <c r="N43" s="74"/>
-      <c r="O43" s="74"/>
-      <c r="P43" s="74"/>
-      <c r="Q43" s="74"/>
-      <c r="R43" s="74"/>
+      <c r="M43" s="73"/>
+      <c r="N43" s="73"/>
+      <c r="O43" s="73"/>
+      <c r="P43" s="73"/>
+      <c r="Q43" s="73"/>
+      <c r="R43" s="73"/>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
@@ -17678,15 +17661,15 @@
       <c r="J45" s="65" t="s">
         <v>171</v>
       </c>
-      <c r="L45" s="73" t="s">
+      <c r="L45" s="72" t="s">
         <v>181</v>
       </c>
-      <c r="M45" s="74"/>
-      <c r="N45" s="74"/>
-      <c r="O45" s="74"/>
-      <c r="P45" s="74"/>
-      <c r="Q45" s="74"/>
-      <c r="R45" s="74"/>
+      <c r="M45" s="73"/>
+      <c r="N45" s="73"/>
+      <c r="O45" s="73"/>
+      <c r="P45" s="73"/>
+      <c r="Q45" s="73"/>
+      <c r="R45" s="73"/>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
@@ -17744,15 +17727,15 @@
       <c r="J47" s="65" t="s">
         <v>172</v>
       </c>
-      <c r="L47" s="73" t="s">
+      <c r="L47" s="72" t="s">
         <v>182</v>
       </c>
-      <c r="M47" s="74"/>
-      <c r="N47" s="74"/>
-      <c r="O47" s="74"/>
-      <c r="P47" s="74"/>
-      <c r="Q47" s="74"/>
-      <c r="R47" s="74"/>
+      <c r="M47" s="73"/>
+      <c r="N47" s="73"/>
+      <c r="O47" s="73"/>
+      <c r="P47" s="73"/>
+      <c r="Q47" s="73"/>
+      <c r="R47" s="73"/>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
@@ -17810,15 +17793,15 @@
       <c r="J49" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="L49" s="73" t="s">
+      <c r="L49" s="72" t="s">
         <v>183</v>
       </c>
-      <c r="M49" s="74"/>
-      <c r="N49" s="74"/>
-      <c r="O49" s="74"/>
-      <c r="P49" s="74"/>
-      <c r="Q49" s="74"/>
-      <c r="R49" s="74"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="73"/>
+      <c r="O49" s="73"/>
+      <c r="P49" s="73"/>
+      <c r="Q49" s="73"/>
+      <c r="R49" s="73"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
@@ -17898,11 +17881,11 @@
       <c r="H52" s="8">
         <v>221850</v>
       </c>
-      <c r="J52" s="75" t="s">
+      <c r="J52" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="K52" s="76"/>
-      <c r="L52" s="76"/>
+      <c r="K52" s="75"/>
+      <c r="L52" s="75"/>
     </row>
     <row r="53" spans="1:18" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
@@ -17967,7 +17950,10 @@
       <c r="J54" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="K54" s="26"/>
+      <c r="K54" s="26" t="str">
+        <f>_xlfn.XLOOKUP(J54, $A$35:$A$60, $G$35:$G$60, "مش موجود", 0, 1)</f>
+        <v>Trading</v>
+      </c>
       <c r="L54" s="11" t="s">
         <v>10</v>
       </c>
@@ -18000,7 +17986,10 @@
       <c r="J55" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="K55" s="26"/>
+      <c r="K55" s="26" t="str">
+        <f t="shared" ref="K55:K59" si="3">_xlfn.XLOOKUP(J55, $A$35:$A$60, $G$35:$G$60, "مش موجود", 0, 1)</f>
+        <v>Oil &amp; Gas</v>
+      </c>
       <c r="L55" s="11" t="s">
         <v>11</v>
       </c>
@@ -18033,7 +18022,10 @@
       <c r="J56" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="26"/>
+      <c r="K56" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>Trading</v>
+      </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
@@ -18063,7 +18055,10 @@
       <c r="J57" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="K57" s="26"/>
+      <c r="K57" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>Trading</v>
+      </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
@@ -18093,7 +18088,10 @@
       <c r="J58" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="K58" s="26"/>
+      <c r="K58" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>Manufacturing</v>
+      </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
@@ -18123,7 +18121,10 @@
       <c r="J59" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="K59" s="66"/>
+      <c r="K59" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>مش موجود</v>
+      </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
@@ -18152,36 +18153,36 @@
       </c>
     </row>
     <row r="66" spans="10:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J66" s="82" t="s">
+      <c r="J66" s="81" t="s">
         <v>188</v>
       </c>
-      <c r="K66" s="83"/>
-      <c r="M66" s="77" t="s">
+      <c r="K66" s="82"/>
+      <c r="M66" s="76" t="s">
         <v>189</v>
       </c>
-      <c r="N66" s="78"/>
+      <c r="N66" s="77"/>
     </row>
     <row r="67" spans="10:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J67" s="84"/>
-      <c r="K67" s="85"/>
+      <c r="J67" s="83"/>
+      <c r="K67" s="84"/>
     </row>
     <row r="68" spans="10:14" ht="18" x14ac:dyDescent="0.3">
-      <c r="M68" s="77" t="s">
+      <c r="M68" s="76" t="s">
         <v>190</v>
       </c>
-      <c r="N68" s="78"/>
+      <c r="N68" s="77"/>
     </row>
     <row r="70" spans="10:14" ht="18" x14ac:dyDescent="0.3">
-      <c r="M70" s="77" t="s">
+      <c r="M70" s="76" t="s">
         <v>191</v>
       </c>
-      <c r="N70" s="78"/>
+      <c r="N70" s="77"/>
     </row>
     <row r="72" spans="10:14" ht="18" x14ac:dyDescent="0.3">
-      <c r="M72" s="77" t="s">
+      <c r="M72" s="76" t="s">
         <v>192</v>
       </c>
-      <c r="N72" s="78"/>
+      <c r="N72" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -18231,35 +18232,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="4:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="E2" s="69">
+      <c r="E2" s="68">
         <v>12.4445</v>
       </c>
     </row>
     <row r="5" spans="4:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="D5" s="68" t="s">
+      <c r="D5" s="67" t="s">
         <v>198</v>
       </c>
-      <c r="E5" s="70">
+      <c r="E5" s="69">
         <f>ROUND(E2,2)</f>
         <v>12.44</v>
       </c>
     </row>
     <row r="6" spans="4:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="67" t="s">
         <v>199</v>
       </c>
-      <c r="E6" s="70">
-        <f>ROUNDUP(E2,1)</f>
-        <v>12.5</v>
+      <c r="E6" s="69">
+        <f>ROUNDUP(E2,2)</f>
+        <v>12.45</v>
       </c>
     </row>
     <row r="7" spans="4:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="D7" s="68" t="s">
+      <c r="D7" s="67" t="s">
         <v>200</v>
       </c>
-      <c r="E7" s="70">
-        <f>ROUNDDOWN(E2,3)</f>
-        <v>12.444000000000001</v>
+      <c r="E7" s="69">
+        <f>ROUNDDOWN(E2,2)</f>
+        <v>12.44</v>
       </c>
     </row>
   </sheetData>
@@ -18276,340 +18277,340 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="67"/>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
+      <c r="A1" s="66"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="66"/>
+      <c r="T1" s="66"/>
+      <c r="U1" s="66"/>
+      <c r="V1" s="66"/>
+      <c r="W1" s="66"/>
+      <c r="X1" s="66"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A2" s="67"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
+      <c r="A2" s="66"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="66"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
+      <c r="U2" s="66"/>
+      <c r="V2" s="66"/>
+      <c r="W2" s="66"/>
+      <c r="X2" s="66"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3" s="67"/>
-      <c r="X3" s="67"/>
+      <c r="A3" s="66"/>
+      <c r="X3" s="66"/>
     </row>
     <row r="4" spans="1:24" ht="18" x14ac:dyDescent="0.3">
-      <c r="A4" s="67"/>
-      <c r="C4" s="104" t="s">
+      <c r="A4" s="66"/>
+      <c r="C4" s="103" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="104"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="104"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="104"/>
-      <c r="L4" s="104"/>
-      <c r="M4" s="104"/>
-      <c r="X4" s="67"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="103"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="103"/>
+      <c r="X4" s="66"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A5" s="67"/>
-      <c r="X5" s="67"/>
+      <c r="A5" s="66"/>
+      <c r="X5" s="66"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A6" s="67"/>
-      <c r="X6" s="67"/>
+      <c r="A6" s="66"/>
+      <c r="X6" s="66"/>
     </row>
     <row r="7" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="67"/>
-      <c r="C7" s="106" t="s">
+      <c r="A7" s="66"/>
+      <c r="C7" s="105" t="s">
         <v>195</v>
       </c>
-      <c r="D7" s="106"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="106"/>
-      <c r="X7" s="67"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="105"/>
+      <c r="K7" s="105"/>
+      <c r="L7" s="105"/>
+      <c r="M7" s="105"/>
+      <c r="X7" s="66"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A8" s="67"/>
-      <c r="X8" s="67"/>
+      <c r="A8" s="66"/>
+      <c r="X8" s="66"/>
     </row>
     <row r="9" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="67"/>
-      <c r="C9" s="106" t="s">
+      <c r="A9" s="66"/>
+      <c r="C9" s="105" t="s">
         <v>196</v>
       </c>
-      <c r="D9" s="106"/>
-      <c r="E9" s="106"/>
-      <c r="F9" s="106"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="106"/>
-      <c r="I9" s="106"/>
-      <c r="J9" s="106"/>
-      <c r="K9" s="106"/>
-      <c r="L9" s="106"/>
-      <c r="M9" s="106"/>
-      <c r="X9" s="67"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="105"/>
+      <c r="M9" s="105"/>
+      <c r="X9" s="66"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A10" s="67"/>
-      <c r="X10" s="67"/>
+      <c r="A10" s="66"/>
+      <c r="X10" s="66"/>
     </row>
     <row r="11" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="67"/>
-      <c r="C11" s="106" t="s">
+      <c r="A11" s="66"/>
+      <c r="C11" s="105" t="s">
         <v>194</v>
       </c>
-      <c r="D11" s="106"/>
-      <c r="E11" s="106"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="106"/>
-      <c r="I11" s="106"/>
-      <c r="J11" s="106"/>
-      <c r="K11" s="106"/>
-      <c r="L11" s="106"/>
-      <c r="M11" s="106"/>
-      <c r="X11" s="67"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="105"/>
+      <c r="I11" s="105"/>
+      <c r="J11" s="105"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="105"/>
+      <c r="M11" s="105"/>
+      <c r="X11" s="66"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A12" s="67"/>
-      <c r="X12" s="67"/>
+      <c r="A12" s="66"/>
+      <c r="X12" s="66"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A13" s="67"/>
-      <c r="X13" s="67"/>
+      <c r="A13" s="66"/>
+      <c r="X13" s="66"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A14" s="67"/>
-      <c r="X14" s="67"/>
+      <c r="A14" s="66"/>
+      <c r="X14" s="66"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A15" s="67"/>
-      <c r="X15" s="67"/>
+      <c r="A15" s="66"/>
+      <c r="X15" s="66"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A16" s="67"/>
-      <c r="X16" s="67"/>
+      <c r="A16" s="66"/>
+      <c r="X16" s="66"/>
     </row>
     <row r="17" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="67"/>
-      <c r="F17" s="105" t="s">
+      <c r="A17" s="66"/>
+      <c r="F17" s="104" t="s">
         <v>197</v>
       </c>
-      <c r="G17" s="105"/>
-      <c r="H17" s="105"/>
-      <c r="I17" s="105"/>
-      <c r="J17" s="105"/>
-      <c r="K17" s="105"/>
-      <c r="L17" s="105"/>
-      <c r="M17" s="105"/>
-      <c r="N17" s="105"/>
-      <c r="O17" s="105"/>
-      <c r="P17" s="105"/>
-      <c r="Q17" s="105"/>
-      <c r="R17" s="105"/>
-      <c r="S17" s="105"/>
-      <c r="T17" s="105"/>
-      <c r="U17" s="105"/>
-      <c r="X17" s="67"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="104"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="104"/>
+      <c r="K17" s="104"/>
+      <c r="L17" s="104"/>
+      <c r="M17" s="104"/>
+      <c r="N17" s="104"/>
+      <c r="O17" s="104"/>
+      <c r="P17" s="104"/>
+      <c r="Q17" s="104"/>
+      <c r="R17" s="104"/>
+      <c r="S17" s="104"/>
+      <c r="T17" s="104"/>
+      <c r="U17" s="104"/>
+      <c r="X17" s="66"/>
     </row>
     <row r="18" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="67"/>
-      <c r="F18" s="105"/>
-      <c r="G18" s="105"/>
-      <c r="H18" s="105"/>
-      <c r="I18" s="105"/>
-      <c r="J18" s="105"/>
-      <c r="K18" s="105"/>
-      <c r="L18" s="105"/>
-      <c r="M18" s="105"/>
-      <c r="N18" s="105"/>
-      <c r="O18" s="105"/>
-      <c r="P18" s="105"/>
-      <c r="Q18" s="105"/>
-      <c r="R18" s="105"/>
-      <c r="S18" s="105"/>
-      <c r="T18" s="105"/>
-      <c r="U18" s="105"/>
-      <c r="X18" s="67"/>
+      <c r="A18" s="66"/>
+      <c r="F18" s="104"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="104"/>
+      <c r="I18" s="104"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="104"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="104"/>
+      <c r="N18" s="104"/>
+      <c r="O18" s="104"/>
+      <c r="P18" s="104"/>
+      <c r="Q18" s="104"/>
+      <c r="R18" s="104"/>
+      <c r="S18" s="104"/>
+      <c r="T18" s="104"/>
+      <c r="U18" s="104"/>
+      <c r="X18" s="66"/>
     </row>
     <row r="19" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="67"/>
-      <c r="F19" s="105"/>
-      <c r="G19" s="105"/>
-      <c r="H19" s="105"/>
-      <c r="I19" s="105"/>
-      <c r="J19" s="105"/>
-      <c r="K19" s="105"/>
-      <c r="L19" s="105"/>
-      <c r="M19" s="105"/>
-      <c r="N19" s="105"/>
-      <c r="O19" s="105"/>
-      <c r="P19" s="105"/>
-      <c r="Q19" s="105"/>
-      <c r="R19" s="105"/>
-      <c r="S19" s="105"/>
-      <c r="T19" s="105"/>
-      <c r="U19" s="105"/>
-      <c r="X19" s="67"/>
+      <c r="A19" s="66"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="104"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="104"/>
+      <c r="K19" s="104"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="104"/>
+      <c r="N19" s="104"/>
+      <c r="O19" s="104"/>
+      <c r="P19" s="104"/>
+      <c r="Q19" s="104"/>
+      <c r="R19" s="104"/>
+      <c r="S19" s="104"/>
+      <c r="T19" s="104"/>
+      <c r="U19" s="104"/>
+      <c r="X19" s="66"/>
     </row>
     <row r="20" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="67"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="105"/>
-      <c r="K20" s="105"/>
-      <c r="L20" s="105"/>
-      <c r="M20" s="105"/>
-      <c r="N20" s="105"/>
-      <c r="O20" s="105"/>
-      <c r="P20" s="105"/>
-      <c r="Q20" s="105"/>
-      <c r="R20" s="105"/>
-      <c r="S20" s="105"/>
-      <c r="T20" s="105"/>
-      <c r="U20" s="105"/>
-      <c r="X20" s="67"/>
+      <c r="A20" s="66"/>
+      <c r="F20" s="104"/>
+      <c r="G20" s="104"/>
+      <c r="H20" s="104"/>
+      <c r="I20" s="104"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="104"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="104"/>
+      <c r="N20" s="104"/>
+      <c r="O20" s="104"/>
+      <c r="P20" s="104"/>
+      <c r="Q20" s="104"/>
+      <c r="R20" s="104"/>
+      <c r="S20" s="104"/>
+      <c r="T20" s="104"/>
+      <c r="U20" s="104"/>
+      <c r="X20" s="66"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A21" s="67"/>
-      <c r="X21" s="67"/>
+      <c r="A21" s="66"/>
+      <c r="X21" s="66"/>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A22" s="67"/>
-      <c r="X22" s="67"/>
+      <c r="A22" s="66"/>
+      <c r="X22" s="66"/>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A23" s="67"/>
-      <c r="X23" s="67"/>
+      <c r="A23" s="66"/>
+      <c r="X23" s="66"/>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A24" s="67"/>
-      <c r="X24" s="67"/>
+      <c r="A24" s="66"/>
+      <c r="X24" s="66"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A25" s="67"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="67"/>
-      <c r="J25" s="67"/>
-      <c r="K25" s="67"/>
-      <c r="L25" s="67"/>
-      <c r="M25" s="67"/>
-      <c r="N25" s="67"/>
-      <c r="O25" s="67"/>
-      <c r="P25" s="67"/>
-      <c r="Q25" s="67"/>
-      <c r="R25" s="67"/>
-      <c r="S25" s="67"/>
-      <c r="T25" s="67"/>
-      <c r="U25" s="67"/>
-      <c r="V25" s="67"/>
-      <c r="W25" s="67"/>
-      <c r="X25" s="67"/>
+      <c r="A25" s="66"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="66"/>
+      <c r="J25" s="66"/>
+      <c r="K25" s="66"/>
+      <c r="L25" s="66"/>
+      <c r="M25" s="66"/>
+      <c r="N25" s="66"/>
+      <c r="O25" s="66"/>
+      <c r="P25" s="66"/>
+      <c r="Q25" s="66"/>
+      <c r="R25" s="66"/>
+      <c r="S25" s="66"/>
+      <c r="T25" s="66"/>
+      <c r="U25" s="66"/>
+      <c r="V25" s="66"/>
+      <c r="W25" s="66"/>
+      <c r="X25" s="66"/>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A26" s="67"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="67"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="67"/>
-      <c r="G26" s="67"/>
-      <c r="H26" s="67"/>
-      <c r="I26" s="67"/>
-      <c r="J26" s="67"/>
-      <c r="K26" s="67"/>
-      <c r="L26" s="67"/>
-      <c r="M26" s="67"/>
-      <c r="N26" s="67"/>
-      <c r="O26" s="67"/>
-      <c r="P26" s="67"/>
-      <c r="Q26" s="67"/>
-      <c r="R26" s="67"/>
-      <c r="S26" s="67"/>
-      <c r="T26" s="67"/>
-      <c r="U26" s="67"/>
-      <c r="V26" s="67"/>
-      <c r="W26" s="67"/>
-      <c r="X26" s="67"/>
+      <c r="A26" s="66"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="66"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="66"/>
+      <c r="J26" s="66"/>
+      <c r="K26" s="66"/>
+      <c r="L26" s="66"/>
+      <c r="M26" s="66"/>
+      <c r="N26" s="66"/>
+      <c r="O26" s="66"/>
+      <c r="P26" s="66"/>
+      <c r="Q26" s="66"/>
+      <c r="R26" s="66"/>
+      <c r="S26" s="66"/>
+      <c r="T26" s="66"/>
+      <c r="U26" s="66"/>
+      <c r="V26" s="66"/>
+      <c r="W26" s="66"/>
+      <c r="X26" s="66"/>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A27" s="67"/>
-      <c r="B27" s="67"/>
-      <c r="C27" s="67"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="67"/>
-      <c r="G27" s="67"/>
-      <c r="H27" s="67"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="67"/>
-      <c r="K27" s="67"/>
-      <c r="L27" s="67"/>
-      <c r="M27" s="67"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="67"/>
-      <c r="P27" s="67"/>
-      <c r="Q27" s="67"/>
-      <c r="R27" s="67"/>
-      <c r="S27" s="67"/>
-      <c r="T27" s="67"/>
-      <c r="U27" s="67"/>
-      <c r="V27" s="67"/>
-      <c r="W27" s="67"/>
-      <c r="X27" s="67"/>
+      <c r="A27" s="66"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="66"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="66"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="66"/>
+      <c r="J27" s="66"/>
+      <c r="K27" s="66"/>
+      <c r="L27" s="66"/>
+      <c r="M27" s="66"/>
+      <c r="N27" s="66"/>
+      <c r="O27" s="66"/>
+      <c r="P27" s="66"/>
+      <c r="Q27" s="66"/>
+      <c r="R27" s="66"/>
+      <c r="S27" s="66"/>
+      <c r="T27" s="66"/>
+      <c r="U27" s="66"/>
+      <c r="V27" s="66"/>
+      <c r="W27" s="66"/>
+      <c r="X27" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="5">
